--- a/public/ImportIngredient.xlsx
+++ b/public/ImportIngredient.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\kaya_bumbu\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BC6EB4-BAA8-4EB0-B987-DE7144A21D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FCD133-D1B0-4C63-9181-9C77250FEBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70C5DD04-4ED6-4560-BA10-02B8C684F989}"/>
   </bookViews>
@@ -833,132 +833,6 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1003,6 +877,132 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1331,10 +1331,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="68">
-        <v>1</v>
-      </c>
-      <c r="B1" s="71" t="s">
+      <c r="A1" s="26">
+        <v>1</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1349,13 +1349,13 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="69"/>
-      <c r="B2" s="72"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="30"/>
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1368,11 +1368,11 @@
       <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="75"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="69"/>
-      <c r="B3" s="72"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="30"/>
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1385,11 +1385,11 @@
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="75"/>
+      <c r="G3" s="33"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="69"/>
-      <c r="B4" s="72"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1402,11 +1402,11 @@
       <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="75"/>
+      <c r="G4" s="33"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="69"/>
-      <c r="B5" s="72"/>
+      <c r="A5" s="27"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1419,11 +1419,11 @@
       <c r="F5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="75"/>
+      <c r="G5" s="33"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="69"/>
-      <c r="B6" s="72"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="30"/>
       <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
@@ -1436,11 +1436,11 @@
       <c r="F6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="75"/>
+      <c r="G6" s="33"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="69"/>
-      <c r="B7" s="72"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="30"/>
       <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
@@ -1453,11 +1453,11 @@
       <c r="F7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="75"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="69"/>
-      <c r="B8" s="72"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
@@ -1470,11 +1470,11 @@
       <c r="F8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="75"/>
+      <c r="G8" s="33"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="69"/>
-      <c r="B9" s="72"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="30"/>
       <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
@@ -1487,11 +1487,11 @@
       <c r="F9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="75"/>
+      <c r="G9" s="33"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="69"/>
-      <c r="B10" s="72"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="30"/>
       <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
@@ -1504,11 +1504,11 @@
       <c r="F10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="75"/>
+      <c r="G10" s="33"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="69"/>
-      <c r="B11" s="72"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
@@ -1521,11 +1521,11 @@
       <c r="F11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="75"/>
+      <c r="G11" s="33"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="69"/>
-      <c r="B12" s="72"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
@@ -1538,11 +1538,11 @@
       <c r="F12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="75"/>
+      <c r="G12" s="33"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="69"/>
-      <c r="B13" s="72"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="3" t="s">
         <v>22</v>
       </c>
@@ -1555,11 +1555,11 @@
       <c r="F13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="75"/>
+      <c r="G13" s="33"/>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="70"/>
-      <c r="B14" s="73"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="31"/>
       <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
@@ -1572,13 +1572,13 @@
       <c r="F14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="76"/>
+      <c r="G14" s="34"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="68">
+      <c r="A15" s="26">
         <v>2</v>
       </c>
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="29" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1593,13 +1593,13 @@
       <c r="F15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="72"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
@@ -1612,11 +1612,11 @@
       <c r="F16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="75"/>
+      <c r="G16" s="33"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="69"/>
-      <c r="B17" s="72"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1629,11 +1629,11 @@
       <c r="F17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="75"/>
+      <c r="G17" s="33"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="69"/>
-      <c r="B18" s="72"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
@@ -1646,11 +1646,11 @@
       <c r="F18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="75"/>
+      <c r="G18" s="33"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="69"/>
-      <c r="B19" s="72"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="3" t="s">
         <v>11</v>
       </c>
@@ -1663,11 +1663,11 @@
       <c r="F19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="75"/>
+      <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="69"/>
-      <c r="B20" s="72"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
@@ -1680,11 +1680,11 @@
       <c r="F20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="75"/>
+      <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="69"/>
-      <c r="B21" s="72"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="3" t="s">
         <v>14</v>
       </c>
@@ -1697,11 +1697,11 @@
       <c r="F21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="75"/>
+      <c r="G21" s="33"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="69"/>
-      <c r="B22" s="72"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="3" t="s">
         <v>16</v>
       </c>
@@ -1714,11 +1714,11 @@
       <c r="F22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="75"/>
+      <c r="G22" s="33"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="69"/>
-      <c r="B23" s="72"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="3" t="s">
         <v>17</v>
       </c>
@@ -1731,11 +1731,11 @@
       <c r="F23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="75"/>
+      <c r="G23" s="33"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="69"/>
-      <c r="B24" s="72"/>
+      <c r="A24" s="27"/>
+      <c r="B24" s="30"/>
       <c r="C24" s="3" t="s">
         <v>18</v>
       </c>
@@ -1748,11 +1748,11 @@
       <c r="F24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="75"/>
+      <c r="G24" s="33"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="69"/>
-      <c r="B25" s="72"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="30"/>
       <c r="C25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1765,11 +1765,11 @@
       <c r="F25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="75"/>
+      <c r="G25" s="33"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="69"/>
-      <c r="B26" s="72"/>
+      <c r="A26" s="27"/>
+      <c r="B26" s="30"/>
       <c r="C26" s="3" t="s">
         <v>21</v>
       </c>
@@ -1782,11 +1782,11 @@
       <c r="F26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="75"/>
+      <c r="G26" s="33"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="69"/>
-      <c r="B27" s="72"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="30"/>
       <c r="C27" s="3" t="s">
         <v>22</v>
       </c>
@@ -1799,11 +1799,11 @@
       <c r="F27" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="75"/>
+      <c r="G27" s="33"/>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="70"/>
-      <c r="B28" s="73"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="31"/>
       <c r="C28" s="5" t="s">
         <v>23</v>
       </c>
@@ -1816,13 +1816,13 @@
       <c r="F28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="76"/>
+      <c r="G28" s="34"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="68">
+      <c r="A29" s="26">
         <v>3</v>
       </c>
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="29" t="s">
         <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -1837,13 +1837,13 @@
       <c r="F29" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="74" t="s">
+      <c r="G29" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="69"/>
-      <c r="B30" s="72"/>
+      <c r="A30" s="27"/>
+      <c r="B30" s="30"/>
       <c r="C30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1856,11 +1856,11 @@
       <c r="F30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G30" s="75"/>
+      <c r="G30" s="33"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="69"/>
-      <c r="B31" s="72"/>
+      <c r="A31" s="27"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="3" t="s">
         <v>28</v>
       </c>
@@ -1873,11 +1873,11 @@
       <c r="F31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G31" s="75"/>
+      <c r="G31" s="33"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="69"/>
-      <c r="B32" s="72"/>
+      <c r="A32" s="27"/>
+      <c r="B32" s="30"/>
       <c r="C32" s="3" t="s">
         <v>29</v>
       </c>
@@ -1890,11 +1890,11 @@
       <c r="F32" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="75"/>
+      <c r="G32" s="33"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="69"/>
-      <c r="B33" s="72"/>
+      <c r="A33" s="27"/>
+      <c r="B33" s="30"/>
       <c r="C33" s="3" t="s">
         <v>30</v>
       </c>
@@ -1907,11 +1907,11 @@
       <c r="F33" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G33" s="75"/>
+      <c r="G33" s="33"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="69"/>
-      <c r="B34" s="72"/>
+      <c r="A34" s="27"/>
+      <c r="B34" s="30"/>
       <c r="C34" s="3" t="s">
         <v>31</v>
       </c>
@@ -1924,11 +1924,11 @@
       <c r="F34" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="75"/>
+      <c r="G34" s="33"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="69"/>
-      <c r="B35" s="72"/>
+      <c r="A35" s="27"/>
+      <c r="B35" s="30"/>
       <c r="C35" s="3" t="s">
         <v>32</v>
       </c>
@@ -1941,11 +1941,11 @@
       <c r="F35" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G35" s="75"/>
+      <c r="G35" s="33"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="69"/>
-      <c r="B36" s="72"/>
+      <c r="A36" s="27"/>
+      <c r="B36" s="30"/>
       <c r="C36" s="3" t="s">
         <v>14</v>
       </c>
@@ -1958,11 +1958,11 @@
       <c r="F36" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G36" s="75"/>
+      <c r="G36" s="33"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="69"/>
-      <c r="B37" s="72"/>
+      <c r="A37" s="27"/>
+      <c r="B37" s="30"/>
       <c r="C37" s="3" t="s">
         <v>33</v>
       </c>
@@ -1975,11 +1975,11 @@
       <c r="F37" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G37" s="75"/>
+      <c r="G37" s="33"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="69"/>
-      <c r="B38" s="72"/>
+      <c r="A38" s="27"/>
+      <c r="B38" s="30"/>
       <c r="C38" s="3" t="s">
         <v>34</v>
       </c>
@@ -1992,11 +1992,11 @@
       <c r="F38" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G38" s="75"/>
+      <c r="G38" s="33"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="69"/>
-      <c r="B39" s="72"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="30"/>
       <c r="C39" s="3" t="s">
         <v>16</v>
       </c>
@@ -2009,11 +2009,11 @@
       <c r="F39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G39" s="75"/>
+      <c r="G39" s="33"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="69"/>
-      <c r="B40" s="72"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="30"/>
       <c r="C40" s="3" t="s">
         <v>17</v>
       </c>
@@ -2026,11 +2026,11 @@
       <c r="F40" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G40" s="75"/>
+      <c r="G40" s="33"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="69"/>
-      <c r="B41" s="72"/>
+      <c r="A41" s="27"/>
+      <c r="B41" s="30"/>
       <c r="C41" s="3" t="s">
         <v>18</v>
       </c>
@@ -2043,11 +2043,11 @@
       <c r="F41" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G41" s="75"/>
+      <c r="G41" s="33"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="69"/>
-      <c r="B42" s="72"/>
+      <c r="A42" s="27"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="3" t="s">
         <v>20</v>
       </c>
@@ -2060,11 +2060,11 @@
       <c r="F42" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G42" s="75"/>
+      <c r="G42" s="33"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="69"/>
-      <c r="B43" s="72"/>
+      <c r="A43" s="27"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
@@ -2077,11 +2077,11 @@
       <c r="F43" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G43" s="75"/>
+      <c r="G43" s="33"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="69"/>
-      <c r="B44" s="72"/>
+      <c r="A44" s="27"/>
+      <c r="B44" s="30"/>
       <c r="C44" s="3" t="s">
         <v>22</v>
       </c>
@@ -2094,11 +2094,11 @@
       <c r="F44" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G44" s="75"/>
+      <c r="G44" s="33"/>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="70"/>
-      <c r="B45" s="73"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="31"/>
       <c r="C45" s="5" t="s">
         <v>23</v>
       </c>
@@ -2111,13 +2111,13 @@
       <c r="F45" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G45" s="76"/>
+      <c r="G45" s="34"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="68">
+      <c r="A46" s="26">
         <v>4</v>
       </c>
-      <c r="B46" s="71" t="s">
+      <c r="B46" s="29" t="s">
         <v>35</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -2132,13 +2132,13 @@
       <c r="F46" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G46" s="74" t="s">
+      <c r="G46" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="69"/>
-      <c r="B47" s="72"/>
+      <c r="A47" s="27"/>
+      <c r="B47" s="30"/>
       <c r="C47" s="3" t="s">
         <v>27</v>
       </c>
@@ -2151,11 +2151,11 @@
       <c r="F47" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="75"/>
+      <c r="G47" s="33"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="69"/>
-      <c r="B48" s="72"/>
+      <c r="A48" s="27"/>
+      <c r="B48" s="30"/>
       <c r="C48" s="3" t="s">
         <v>28</v>
       </c>
@@ -2168,11 +2168,11 @@
       <c r="F48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G48" s="75"/>
+      <c r="G48" s="33"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="69"/>
-      <c r="B49" s="72"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="30"/>
       <c r="C49" s="3" t="s">
         <v>29</v>
       </c>
@@ -2185,11 +2185,11 @@
       <c r="F49" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G49" s="75"/>
+      <c r="G49" s="33"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="69"/>
-      <c r="B50" s="72"/>
+      <c r="A50" s="27"/>
+      <c r="B50" s="30"/>
       <c r="C50" s="3" t="s">
         <v>30</v>
       </c>
@@ -2202,11 +2202,11 @@
       <c r="F50" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G50" s="75"/>
+      <c r="G50" s="33"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="69"/>
-      <c r="B51" s="72"/>
+      <c r="A51" s="27"/>
+      <c r="B51" s="30"/>
       <c r="C51" s="3" t="s">
         <v>31</v>
       </c>
@@ -2219,11 +2219,11 @@
       <c r="F51" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G51" s="75"/>
+      <c r="G51" s="33"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="69"/>
-      <c r="B52" s="72"/>
+      <c r="A52" s="27"/>
+      <c r="B52" s="30"/>
       <c r="C52" s="3" t="s">
         <v>32</v>
       </c>
@@ -2236,11 +2236,11 @@
       <c r="F52" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G52" s="75"/>
+      <c r="G52" s="33"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="69"/>
-      <c r="B53" s="72"/>
+      <c r="A53" s="27"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="3" t="s">
         <v>14</v>
       </c>
@@ -2253,11 +2253,11 @@
       <c r="F53" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G53" s="75"/>
+      <c r="G53" s="33"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="69"/>
-      <c r="B54" s="72"/>
+      <c r="A54" s="27"/>
+      <c r="B54" s="30"/>
       <c r="C54" s="3" t="s">
         <v>33</v>
       </c>
@@ -2270,11 +2270,11 @@
       <c r="F54" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G54" s="75"/>
+      <c r="G54" s="33"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="69"/>
-      <c r="B55" s="72"/>
+      <c r="A55" s="27"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="3" t="s">
         <v>34</v>
       </c>
@@ -2287,11 +2287,11 @@
       <c r="F55" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G55" s="75"/>
+      <c r="G55" s="33"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="69"/>
-      <c r="B56" s="72"/>
+      <c r="A56" s="27"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
@@ -2304,11 +2304,11 @@
       <c r="F56" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G56" s="75"/>
+      <c r="G56" s="33"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="69"/>
-      <c r="B57" s="72"/>
+      <c r="A57" s="27"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2321,11 +2321,11 @@
       <c r="F57" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G57" s="75"/>
+      <c r="G57" s="33"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="69"/>
-      <c r="B58" s="72"/>
+      <c r="A58" s="27"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2338,11 +2338,11 @@
       <c r="F58" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="75"/>
+      <c r="G58" s="33"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="69"/>
-      <c r="B59" s="72"/>
+      <c r="A59" s="27"/>
+      <c r="B59" s="30"/>
       <c r="C59" s="3" t="s">
         <v>20</v>
       </c>
@@ -2355,11 +2355,11 @@
       <c r="F59" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G59" s="75"/>
+      <c r="G59" s="33"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="69"/>
-      <c r="B60" s="72"/>
+      <c r="A60" s="27"/>
+      <c r="B60" s="30"/>
       <c r="C60" s="3" t="s">
         <v>21</v>
       </c>
@@ -2372,11 +2372,11 @@
       <c r="F60" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G60" s="75"/>
+      <c r="G60" s="33"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="69"/>
-      <c r="B61" s="72"/>
+      <c r="A61" s="27"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="3" t="s">
         <v>22</v>
       </c>
@@ -2389,11 +2389,11 @@
       <c r="F61" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G61" s="75"/>
+      <c r="G61" s="33"/>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="70"/>
-      <c r="B62" s="73"/>
+      <c r="A62" s="28"/>
+      <c r="B62" s="31"/>
       <c r="C62" s="5" t="s">
         <v>23</v>
       </c>
@@ -2406,13 +2406,13 @@
       <c r="F62" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G62" s="76"/>
+      <c r="G62" s="34"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="68">
+      <c r="A63" s="26">
         <v>5</v>
       </c>
-      <c r="B63" s="80" t="s">
+      <c r="B63" s="38" t="s">
         <v>36</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -2427,13 +2427,13 @@
       <c r="F63" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G63" s="74" t="s">
+      <c r="G63" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="69"/>
-      <c r="B64" s="81"/>
+      <c r="A64" s="27"/>
+      <c r="B64" s="39"/>
       <c r="C64" s="3" t="s">
         <v>37</v>
       </c>
@@ -2446,11 +2446,11 @@
       <c r="F64" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G64" s="75"/>
+      <c r="G64" s="33"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="69"/>
-      <c r="B65" s="81"/>
+      <c r="A65" s="27"/>
+      <c r="B65" s="39"/>
       <c r="C65" s="3" t="s">
         <v>28</v>
       </c>
@@ -2463,11 +2463,11 @@
       <c r="F65" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G65" s="75"/>
+      <c r="G65" s="33"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="69"/>
-      <c r="B66" s="81"/>
+      <c r="A66" s="27"/>
+      <c r="B66" s="39"/>
       <c r="C66" s="3" t="s">
         <v>29</v>
       </c>
@@ -2480,11 +2480,11 @@
       <c r="F66" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G66" s="75"/>
+      <c r="G66" s="33"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="69"/>
-      <c r="B67" s="81"/>
+      <c r="A67" s="27"/>
+      <c r="B67" s="39"/>
       <c r="C67" s="3" t="s">
         <v>30</v>
       </c>
@@ -2497,11 +2497,11 @@
       <c r="F67" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G67" s="75"/>
+      <c r="G67" s="33"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="69"/>
-      <c r="B68" s="81"/>
+      <c r="A68" s="27"/>
+      <c r="B68" s="39"/>
       <c r="C68" s="3" t="s">
         <v>31</v>
       </c>
@@ -2514,11 +2514,11 @@
       <c r="F68" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G68" s="75"/>
+      <c r="G68" s="33"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="69"/>
-      <c r="B69" s="81"/>
+      <c r="A69" s="27"/>
+      <c r="B69" s="39"/>
       <c r="C69" s="3" t="s">
         <v>32</v>
       </c>
@@ -2531,11 +2531,11 @@
       <c r="F69" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G69" s="75"/>
+      <c r="G69" s="33"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="69"/>
-      <c r="B70" s="81"/>
+      <c r="A70" s="27"/>
+      <c r="B70" s="39"/>
       <c r="C70" s="3" t="s">
         <v>14</v>
       </c>
@@ -2548,11 +2548,11 @@
       <c r="F70" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G70" s="75"/>
+      <c r="G70" s="33"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="69"/>
-      <c r="B71" s="81"/>
+      <c r="A71" s="27"/>
+      <c r="B71" s="39"/>
       <c r="C71" s="3" t="s">
         <v>33</v>
       </c>
@@ -2565,11 +2565,11 @@
       <c r="F71" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G71" s="75"/>
+      <c r="G71" s="33"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="69"/>
-      <c r="B72" s="81"/>
+      <c r="A72" s="27"/>
+      <c r="B72" s="39"/>
       <c r="C72" s="3" t="s">
         <v>34</v>
       </c>
@@ -2582,11 +2582,11 @@
       <c r="F72" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G72" s="75"/>
+      <c r="G72" s="33"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="69"/>
-      <c r="B73" s="81"/>
+      <c r="A73" s="27"/>
+      <c r="B73" s="39"/>
       <c r="C73" s="3" t="s">
         <v>16</v>
       </c>
@@ -2599,11 +2599,11 @@
       <c r="F73" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G73" s="75"/>
+      <c r="G73" s="33"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="69"/>
-      <c r="B74" s="81"/>
+      <c r="A74" s="27"/>
+      <c r="B74" s="39"/>
       <c r="C74" s="3" t="s">
         <v>17</v>
       </c>
@@ -2616,11 +2616,11 @@
       <c r="F74" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G74" s="75"/>
+      <c r="G74" s="33"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="69"/>
-      <c r="B75" s="81"/>
+      <c r="A75" s="27"/>
+      <c r="B75" s="39"/>
       <c r="C75" s="3" t="s">
         <v>18</v>
       </c>
@@ -2633,11 +2633,11 @@
       <c r="F75" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G75" s="75"/>
+      <c r="G75" s="33"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="69"/>
-      <c r="B76" s="81"/>
+      <c r="A76" s="27"/>
+      <c r="B76" s="39"/>
       <c r="C76" s="3" t="s">
         <v>20</v>
       </c>
@@ -2650,11 +2650,11 @@
       <c r="F76" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G76" s="75"/>
+      <c r="G76" s="33"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="69"/>
-      <c r="B77" s="81"/>
+      <c r="A77" s="27"/>
+      <c r="B77" s="39"/>
       <c r="C77" s="3" t="s">
         <v>21</v>
       </c>
@@ -2667,11 +2667,11 @@
       <c r="F77" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G77" s="75"/>
+      <c r="G77" s="33"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="69"/>
-      <c r="B78" s="81"/>
+      <c r="A78" s="27"/>
+      <c r="B78" s="39"/>
       <c r="C78" s="3" t="s">
         <v>22</v>
       </c>
@@ -2684,11 +2684,11 @@
       <c r="F78" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G78" s="75"/>
+      <c r="G78" s="33"/>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="70"/>
-      <c r="B79" s="82"/>
+      <c r="A79" s="28"/>
+      <c r="B79" s="40"/>
       <c r="C79" s="5" t="s">
         <v>23</v>
       </c>
@@ -2701,13 +2701,13 @@
       <c r="F79" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G79" s="76"/>
+      <c r="G79" s="34"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="68">
-        <v>6</v>
-      </c>
-      <c r="B80" s="80" t="s">
+      <c r="A80" s="26">
+        <v>6</v>
+      </c>
+      <c r="B80" s="38" t="s">
         <v>38</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -2722,13 +2722,13 @@
       <c r="F80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G80" s="74" t="s">
+      <c r="G80" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="69"/>
-      <c r="B81" s="81"/>
+      <c r="A81" s="27"/>
+      <c r="B81" s="39"/>
       <c r="C81" s="3" t="s">
         <v>37</v>
       </c>
@@ -2741,11 +2741,11 @@
       <c r="F81" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G81" s="75"/>
+      <c r="G81" s="33"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="69"/>
-      <c r="B82" s="81"/>
+      <c r="A82" s="27"/>
+      <c r="B82" s="39"/>
       <c r="C82" s="3" t="s">
         <v>28</v>
       </c>
@@ -2758,11 +2758,11 @@
       <c r="F82" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G82" s="75"/>
+      <c r="G82" s="33"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="69"/>
-      <c r="B83" s="81"/>
+      <c r="A83" s="27"/>
+      <c r="B83" s="39"/>
       <c r="C83" s="3" t="s">
         <v>29</v>
       </c>
@@ -2775,11 +2775,11 @@
       <c r="F83" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G83" s="75"/>
+      <c r="G83" s="33"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="69"/>
-      <c r="B84" s="81"/>
+      <c r="A84" s="27"/>
+      <c r="B84" s="39"/>
       <c r="C84" s="3" t="s">
         <v>30</v>
       </c>
@@ -2792,11 +2792,11 @@
       <c r="F84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="75"/>
+      <c r="G84" s="33"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="69"/>
-      <c r="B85" s="81"/>
+      <c r="A85" s="27"/>
+      <c r="B85" s="39"/>
       <c r="C85" s="3" t="s">
         <v>31</v>
       </c>
@@ -2809,11 +2809,11 @@
       <c r="F85" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G85" s="75"/>
+      <c r="G85" s="33"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="69"/>
-      <c r="B86" s="81"/>
+      <c r="A86" s="27"/>
+      <c r="B86" s="39"/>
       <c r="C86" s="3" t="s">
         <v>32</v>
       </c>
@@ -2826,11 +2826,11 @@
       <c r="F86" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G86" s="75"/>
+      <c r="G86" s="33"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="69"/>
-      <c r="B87" s="81"/>
+      <c r="A87" s="27"/>
+      <c r="B87" s="39"/>
       <c r="C87" s="3" t="s">
         <v>14</v>
       </c>
@@ -2843,11 +2843,11 @@
       <c r="F87" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G87" s="75"/>
+      <c r="G87" s="33"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="69"/>
-      <c r="B88" s="81"/>
+      <c r="A88" s="27"/>
+      <c r="B88" s="39"/>
       <c r="C88" s="3" t="s">
         <v>33</v>
       </c>
@@ -2860,11 +2860,11 @@
       <c r="F88" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G88" s="75"/>
+      <c r="G88" s="33"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="69"/>
-      <c r="B89" s="81"/>
+      <c r="A89" s="27"/>
+      <c r="B89" s="39"/>
       <c r="C89" s="3" t="s">
         <v>34</v>
       </c>
@@ -2877,11 +2877,11 @@
       <c r="F89" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G89" s="75"/>
+      <c r="G89" s="33"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="69"/>
-      <c r="B90" s="81"/>
+      <c r="A90" s="27"/>
+      <c r="B90" s="39"/>
       <c r="C90" s="3" t="s">
         <v>16</v>
       </c>
@@ -2894,11 +2894,11 @@
       <c r="F90" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G90" s="75"/>
+      <c r="G90" s="33"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="69"/>
-      <c r="B91" s="81"/>
+      <c r="A91" s="27"/>
+      <c r="B91" s="39"/>
       <c r="C91" s="3" t="s">
         <v>17</v>
       </c>
@@ -2911,11 +2911,11 @@
       <c r="F91" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G91" s="75"/>
+      <c r="G91" s="33"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="69"/>
-      <c r="B92" s="81"/>
+      <c r="A92" s="27"/>
+      <c r="B92" s="39"/>
       <c r="C92" s="3" t="s">
         <v>18</v>
       </c>
@@ -2928,11 +2928,11 @@
       <c r="F92" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G92" s="75"/>
+      <c r="G92" s="33"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="69"/>
-      <c r="B93" s="81"/>
+      <c r="A93" s="27"/>
+      <c r="B93" s="39"/>
       <c r="C93" s="3" t="s">
         <v>20</v>
       </c>
@@ -2945,11 +2945,11 @@
       <c r="F93" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G93" s="75"/>
+      <c r="G93" s="33"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="69"/>
-      <c r="B94" s="81"/>
+      <c r="A94" s="27"/>
+      <c r="B94" s="39"/>
       <c r="C94" s="3" t="s">
         <v>21</v>
       </c>
@@ -2962,11 +2962,11 @@
       <c r="F94" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G94" s="75"/>
+      <c r="G94" s="33"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="69"/>
-      <c r="B95" s="81"/>
+      <c r="A95" s="27"/>
+      <c r="B95" s="39"/>
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
@@ -2979,11 +2979,11 @@
       <c r="F95" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G95" s="75"/>
+      <c r="G95" s="33"/>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
-      <c r="B96" s="82"/>
+      <c r="A96" s="28"/>
+      <c r="B96" s="40"/>
       <c r="C96" s="5" t="s">
         <v>23</v>
       </c>
@@ -2996,13 +2996,13 @@
       <c r="F96" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G96" s="76"/>
+      <c r="G96" s="34"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="68">
+      <c r="A97" s="26">
         <v>7</v>
       </c>
-      <c r="B97" s="77" t="s">
+      <c r="B97" s="35" t="s">
         <v>39</v>
       </c>
       <c r="C97" s="1" t="s">
@@ -3017,13 +3017,13 @@
       <c r="F97" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G97" s="74" t="s">
+      <c r="G97" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="69"/>
-      <c r="B98" s="78"/>
+      <c r="A98" s="27"/>
+      <c r="B98" s="36"/>
       <c r="C98" s="3" t="s">
         <v>41</v>
       </c>
@@ -3036,11 +3036,11 @@
       <c r="F98" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G98" s="75"/>
+      <c r="G98" s="33"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="69"/>
-      <c r="B99" s="78"/>
+      <c r="A99" s="27"/>
+      <c r="B99" s="36"/>
       <c r="C99" s="3" t="s">
         <v>42</v>
       </c>
@@ -3053,11 +3053,11 @@
       <c r="F99" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G99" s="75"/>
+      <c r="G99" s="33"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="69"/>
-      <c r="B100" s="78"/>
+      <c r="A100" s="27"/>
+      <c r="B100" s="36"/>
       <c r="C100" s="3" t="s">
         <v>43</v>
       </c>
@@ -3070,11 +3070,11 @@
       <c r="F100" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G100" s="75"/>
+      <c r="G100" s="33"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="69"/>
-      <c r="B101" s="78"/>
+      <c r="A101" s="27"/>
+      <c r="B101" s="36"/>
       <c r="C101" s="3" t="s">
         <v>44</v>
       </c>
@@ -3087,11 +3087,11 @@
       <c r="F101" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G101" s="75"/>
+      <c r="G101" s="33"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="69"/>
-      <c r="B102" s="78"/>
+      <c r="A102" s="27"/>
+      <c r="B102" s="36"/>
       <c r="C102" s="3" t="s">
         <v>13</v>
       </c>
@@ -3104,11 +3104,11 @@
       <c r="F102" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G102" s="75"/>
+      <c r="G102" s="33"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="69"/>
-      <c r="B103" s="78"/>
+      <c r="A103" s="27"/>
+      <c r="B103" s="36"/>
       <c r="C103" s="3" t="s">
         <v>32</v>
       </c>
@@ -3121,11 +3121,11 @@
       <c r="F103" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G103" s="75"/>
+      <c r="G103" s="33"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="69"/>
-      <c r="B104" s="78"/>
+      <c r="A104" s="27"/>
+      <c r="B104" s="36"/>
       <c r="C104" s="3" t="s">
         <v>14</v>
       </c>
@@ -3138,11 +3138,11 @@
       <c r="F104" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G104" s="75"/>
+      <c r="G104" s="33"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="69"/>
-      <c r="B105" s="78"/>
+      <c r="A105" s="27"/>
+      <c r="B105" s="36"/>
       <c r="C105" s="3" t="s">
         <v>33</v>
       </c>
@@ -3155,11 +3155,11 @@
       <c r="F105" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G105" s="75"/>
+      <c r="G105" s="33"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="69"/>
-      <c r="B106" s="78"/>
+      <c r="A106" s="27"/>
+      <c r="B106" s="36"/>
       <c r="C106" s="3" t="s">
         <v>34</v>
       </c>
@@ -3172,11 +3172,11 @@
       <c r="F106" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G106" s="75"/>
+      <c r="G106" s="33"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="69"/>
-      <c r="B107" s="78"/>
+      <c r="A107" s="27"/>
+      <c r="B107" s="36"/>
       <c r="C107" s="3" t="s">
         <v>16</v>
       </c>
@@ -3189,11 +3189,11 @@
       <c r="F107" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G107" s="75"/>
+      <c r="G107" s="33"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="69"/>
-      <c r="B108" s="78"/>
+      <c r="A108" s="27"/>
+      <c r="B108" s="36"/>
       <c r="C108" s="3" t="s">
         <v>17</v>
       </c>
@@ -3206,11 +3206,11 @@
       <c r="F108" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G108" s="75"/>
+      <c r="G108" s="33"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="69"/>
-      <c r="B109" s="78"/>
+      <c r="A109" s="27"/>
+      <c r="B109" s="36"/>
       <c r="C109" s="3" t="s">
         <v>18</v>
       </c>
@@ -3223,11 +3223,11 @@
       <c r="F109" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G109" s="75"/>
+      <c r="G109" s="33"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="69"/>
-      <c r="B110" s="78"/>
+      <c r="A110" s="27"/>
+      <c r="B110" s="36"/>
       <c r="C110" s="3" t="s">
         <v>20</v>
       </c>
@@ -3240,11 +3240,11 @@
       <c r="F110" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G110" s="75"/>
+      <c r="G110" s="33"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="69"/>
-      <c r="B111" s="78"/>
+      <c r="A111" s="27"/>
+      <c r="B111" s="36"/>
       <c r="C111" s="3" t="s">
         <v>21</v>
       </c>
@@ -3257,11 +3257,11 @@
       <c r="F111" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G111" s="75"/>
+      <c r="G111" s="33"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="69"/>
-      <c r="B112" s="78"/>
+      <c r="A112" s="27"/>
+      <c r="B112" s="36"/>
       <c r="C112" s="3" t="s">
         <v>22</v>
       </c>
@@ -3274,11 +3274,11 @@
       <c r="F112" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G112" s="75"/>
+      <c r="G112" s="33"/>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="70"/>
-      <c r="B113" s="79"/>
+      <c r="A113" s="28"/>
+      <c r="B113" s="37"/>
       <c r="C113" s="5" t="s">
         <v>23</v>
       </c>
@@ -3291,13 +3291,13 @@
       <c r="F113" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G113" s="76"/>
+      <c r="G113" s="34"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="68">
+      <c r="A114" s="26">
         <v>8</v>
       </c>
-      <c r="B114" s="80" t="s">
+      <c r="B114" s="38" t="s">
         <v>45</v>
       </c>
       <c r="C114" s="1" t="s">
@@ -3312,13 +3312,13 @@
       <c r="F114" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G114" s="74" t="s">
+      <c r="G114" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="69"/>
-      <c r="B115" s="81"/>
+      <c r="A115" s="27"/>
+      <c r="B115" s="39"/>
       <c r="C115" s="3" t="s">
         <v>5</v>
       </c>
@@ -3331,11 +3331,11 @@
       <c r="F115" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G115" s="75"/>
+      <c r="G115" s="33"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="69"/>
-      <c r="B116" s="81"/>
+      <c r="A116" s="27"/>
+      <c r="B116" s="39"/>
       <c r="C116" s="3" t="s">
         <v>47</v>
       </c>
@@ -3348,11 +3348,11 @@
       <c r="F116" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G116" s="75"/>
+      <c r="G116" s="33"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="69"/>
-      <c r="B117" s="81"/>
+      <c r="A117" s="27"/>
+      <c r="B117" s="39"/>
       <c r="C117" s="3" t="s">
         <v>48</v>
       </c>
@@ -3365,11 +3365,11 @@
       <c r="F117" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G117" s="75"/>
+      <c r="G117" s="33"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="69"/>
-      <c r="B118" s="81"/>
+      <c r="A118" s="27"/>
+      <c r="B118" s="39"/>
       <c r="C118" s="3" t="s">
         <v>49</v>
       </c>
@@ -3382,11 +3382,11 @@
       <c r="F118" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G118" s="75"/>
+      <c r="G118" s="33"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="69"/>
-      <c r="B119" s="81"/>
+      <c r="A119" s="27"/>
+      <c r="B119" s="39"/>
       <c r="C119" s="3" t="s">
         <v>50</v>
       </c>
@@ -3399,11 +3399,11 @@
       <c r="F119" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G119" s="75"/>
+      <c r="G119" s="33"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="69"/>
-      <c r="B120" s="81"/>
+      <c r="A120" s="27"/>
+      <c r="B120" s="39"/>
       <c r="C120" s="3" t="s">
         <v>13</v>
       </c>
@@ -3416,11 +3416,11 @@
       <c r="F120" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G120" s="75"/>
+      <c r="G120" s="33"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="69"/>
-      <c r="B121" s="81"/>
+      <c r="A121" s="27"/>
+      <c r="B121" s="39"/>
       <c r="C121" s="3" t="s">
         <v>14</v>
       </c>
@@ -3433,11 +3433,11 @@
       <c r="F121" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G121" s="75"/>
+      <c r="G121" s="33"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="69"/>
-      <c r="B122" s="81"/>
+      <c r="A122" s="27"/>
+      <c r="B122" s="39"/>
       <c r="C122" s="3" t="s">
         <v>16</v>
       </c>
@@ -3450,11 +3450,11 @@
       <c r="F122" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G122" s="75"/>
+      <c r="G122" s="33"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="69"/>
-      <c r="B123" s="81"/>
+      <c r="A123" s="27"/>
+      <c r="B123" s="39"/>
       <c r="C123" s="3" t="s">
         <v>34</v>
       </c>
@@ -3467,11 +3467,11 @@
       <c r="F123" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G123" s="75"/>
+      <c r="G123" s="33"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="69"/>
-      <c r="B124" s="81"/>
+      <c r="A124" s="27"/>
+      <c r="B124" s="39"/>
       <c r="C124" s="3" t="s">
         <v>33</v>
       </c>
@@ -3484,11 +3484,11 @@
       <c r="F124" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G124" s="75"/>
+      <c r="G124" s="33"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="69"/>
-      <c r="B125" s="81"/>
+      <c r="A125" s="27"/>
+      <c r="B125" s="39"/>
       <c r="C125" s="3" t="s">
         <v>17</v>
       </c>
@@ -3501,11 +3501,11 @@
       <c r="F125" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G125" s="75"/>
+      <c r="G125" s="33"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="69"/>
-      <c r="B126" s="81"/>
+      <c r="A126" s="27"/>
+      <c r="B126" s="39"/>
       <c r="C126" s="3" t="s">
         <v>18</v>
       </c>
@@ -3518,11 +3518,11 @@
       <c r="F126" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G126" s="75"/>
+      <c r="G126" s="33"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="69"/>
-      <c r="B127" s="81"/>
+      <c r="A127" s="27"/>
+      <c r="B127" s="39"/>
       <c r="C127" s="3" t="s">
         <v>20</v>
       </c>
@@ -3535,11 +3535,11 @@
       <c r="F127" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G127" s="75"/>
+      <c r="G127" s="33"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="69"/>
-      <c r="B128" s="81"/>
+      <c r="A128" s="27"/>
+      <c r="B128" s="39"/>
       <c r="C128" s="3" t="s">
         <v>21</v>
       </c>
@@ -3552,11 +3552,11 @@
       <c r="F128" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G128" s="75"/>
+      <c r="G128" s="33"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="69"/>
-      <c r="B129" s="81"/>
+      <c r="A129" s="27"/>
+      <c r="B129" s="39"/>
       <c r="C129" s="3" t="s">
         <v>22</v>
       </c>
@@ -3569,11 +3569,11 @@
       <c r="F129" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G129" s="75"/>
+      <c r="G129" s="33"/>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="70"/>
-      <c r="B130" s="82"/>
+      <c r="A130" s="28"/>
+      <c r="B130" s="40"/>
       <c r="C130" s="5" t="s">
         <v>23</v>
       </c>
@@ -3586,13 +3586,13 @@
       <c r="F130" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G130" s="76"/>
+      <c r="G130" s="34"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="68">
-        <v>9</v>
-      </c>
-      <c r="B131" s="71" t="s">
+      <c r="A131" s="26">
+        <v>9</v>
+      </c>
+      <c r="B131" s="29" t="s">
         <v>51</v>
       </c>
       <c r="C131" s="1" t="s">
@@ -3607,13 +3607,13 @@
       <c r="F131" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G131" s="74" t="s">
+      <c r="G131" s="32" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="69"/>
-      <c r="B132" s="72"/>
+      <c r="A132" s="27"/>
+      <c r="B132" s="30"/>
       <c r="C132" s="3" t="s">
         <v>52</v>
       </c>
@@ -3626,11 +3626,11 @@
       <c r="F132" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G132" s="75"/>
+      <c r="G132" s="33"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="69"/>
-      <c r="B133" s="72"/>
+      <c r="A133" s="27"/>
+      <c r="B133" s="30"/>
       <c r="C133" s="3" t="s">
         <v>53</v>
       </c>
@@ -3643,11 +3643,11 @@
       <c r="F133" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G133" s="75"/>
+      <c r="G133" s="33"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="69"/>
-      <c r="B134" s="72"/>
+      <c r="A134" s="27"/>
+      <c r="B134" s="30"/>
       <c r="C134" s="3" t="s">
         <v>47</v>
       </c>
@@ -3660,11 +3660,11 @@
       <c r="F134" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G134" s="75"/>
+      <c r="G134" s="33"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="69"/>
-      <c r="B135" s="72"/>
+      <c r="A135" s="27"/>
+      <c r="B135" s="30"/>
       <c r="C135" s="3" t="s">
         <v>48</v>
       </c>
@@ -3677,11 +3677,11 @@
       <c r="F135" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G135" s="75"/>
+      <c r="G135" s="33"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="69"/>
-      <c r="B136" s="72"/>
+      <c r="A136" s="27"/>
+      <c r="B136" s="30"/>
       <c r="C136" s="3" t="s">
         <v>49</v>
       </c>
@@ -3694,11 +3694,11 @@
       <c r="F136" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G136" s="75"/>
+      <c r="G136" s="33"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="69"/>
-      <c r="B137" s="72"/>
+      <c r="A137" s="27"/>
+      <c r="B137" s="30"/>
       <c r="C137" s="3" t="s">
         <v>50</v>
       </c>
@@ -3711,11 +3711,11 @@
       <c r="F137" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G137" s="75"/>
+      <c r="G137" s="33"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="69"/>
-      <c r="B138" s="72"/>
+      <c r="A138" s="27"/>
+      <c r="B138" s="30"/>
       <c r="C138" s="3" t="s">
         <v>13</v>
       </c>
@@ -3728,11 +3728,11 @@
       <c r="F138" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G138" s="75"/>
+      <c r="G138" s="33"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="69"/>
-      <c r="B139" s="72"/>
+      <c r="A139" s="27"/>
+      <c r="B139" s="30"/>
       <c r="C139" s="3" t="s">
         <v>14</v>
       </c>
@@ -3745,11 +3745,11 @@
       <c r="F139" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G139" s="75"/>
+      <c r="G139" s="33"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="69"/>
-      <c r="B140" s="72"/>
+      <c r="A140" s="27"/>
+      <c r="B140" s="30"/>
       <c r="C140" s="3" t="s">
         <v>16</v>
       </c>
@@ -3762,11 +3762,11 @@
       <c r="F140" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G140" s="75"/>
+      <c r="G140" s="33"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="69"/>
-      <c r="B141" s="72"/>
+      <c r="A141" s="27"/>
+      <c r="B141" s="30"/>
       <c r="C141" s="3" t="s">
         <v>34</v>
       </c>
@@ -3779,11 +3779,11 @@
       <c r="F141" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G141" s="75"/>
+      <c r="G141" s="33"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="69"/>
-      <c r="B142" s="72"/>
+      <c r="A142" s="27"/>
+      <c r="B142" s="30"/>
       <c r="C142" s="3" t="s">
         <v>33</v>
       </c>
@@ -3796,11 +3796,11 @@
       <c r="F142" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G142" s="75"/>
+      <c r="G142" s="33"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="69"/>
-      <c r="B143" s="72"/>
+      <c r="A143" s="27"/>
+      <c r="B143" s="30"/>
       <c r="C143" s="3" t="s">
         <v>17</v>
       </c>
@@ -3813,11 +3813,11 @@
       <c r="F143" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G143" s="75"/>
+      <c r="G143" s="33"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="69"/>
-      <c r="B144" s="72"/>
+      <c r="A144" s="27"/>
+      <c r="B144" s="30"/>
       <c r="C144" s="3" t="s">
         <v>18</v>
       </c>
@@ -3830,11 +3830,11 @@
       <c r="F144" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G144" s="75"/>
+      <c r="G144" s="33"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="69"/>
-      <c r="B145" s="72"/>
+      <c r="A145" s="27"/>
+      <c r="B145" s="30"/>
       <c r="C145" s="3" t="s">
         <v>20</v>
       </c>
@@ -3847,11 +3847,11 @@
       <c r="F145" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G145" s="75"/>
+      <c r="G145" s="33"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="69"/>
-      <c r="B146" s="72"/>
+      <c r="A146" s="27"/>
+      <c r="B146" s="30"/>
       <c r="C146" s="3" t="s">
         <v>21</v>
       </c>
@@ -3864,11 +3864,11 @@
       <c r="F146" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="75"/>
+      <c r="G146" s="33"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="69"/>
-      <c r="B147" s="72"/>
+      <c r="A147" s="27"/>
+      <c r="B147" s="30"/>
       <c r="C147" s="3" t="s">
         <v>22</v>
       </c>
@@ -3881,11 +3881,11 @@
       <c r="F147" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G147" s="75"/>
+      <c r="G147" s="33"/>
     </row>
     <row r="148" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="70"/>
-      <c r="B148" s="73"/>
+      <c r="A148" s="28"/>
+      <c r="B148" s="31"/>
       <c r="C148" s="5" t="s">
         <v>23</v>
       </c>
@@ -3898,13 +3898,13 @@
       <c r="F148" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G148" s="76"/>
+      <c r="G148" s="34"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="47">
+      <c r="A149" s="50">
         <v>10</v>
       </c>
-      <c r="B149" s="65" t="s">
+      <c r="B149" s="44" t="s">
         <v>54</v>
       </c>
       <c r="C149" s="7" t="s">
@@ -3919,13 +3919,13 @@
       <c r="F149" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G149" s="53" t="s">
+      <c r="G149" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="48"/>
-      <c r="B150" s="66"/>
+      <c r="A150" s="51"/>
+      <c r="B150" s="45"/>
       <c r="C150" s="9" t="s">
         <v>5</v>
       </c>
@@ -3938,11 +3938,11 @@
       <c r="F150" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G150" s="54"/>
+      <c r="G150" s="48"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="48"/>
-      <c r="B151" s="66"/>
+      <c r="A151" s="51"/>
+      <c r="B151" s="45"/>
       <c r="C151" s="9" t="s">
         <v>8</v>
       </c>
@@ -3955,11 +3955,11 @@
       <c r="F151" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G151" s="54"/>
+      <c r="G151" s="48"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="48"/>
-      <c r="B152" s="66"/>
+      <c r="A152" s="51"/>
+      <c r="B152" s="45"/>
       <c r="C152" s="9" t="s">
         <v>10</v>
       </c>
@@ -3972,11 +3972,11 @@
       <c r="F152" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G152" s="54"/>
+      <c r="G152" s="48"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" s="48"/>
-      <c r="B153" s="66"/>
+      <c r="A153" s="51"/>
+      <c r="B153" s="45"/>
       <c r="C153" s="9" t="s">
         <v>11</v>
       </c>
@@ -3989,11 +3989,11 @@
       <c r="F153" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G153" s="54"/>
+      <c r="G153" s="48"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" s="48"/>
-      <c r="B154" s="66"/>
+      <c r="A154" s="51"/>
+      <c r="B154" s="45"/>
       <c r="C154" s="9" t="s">
         <v>13</v>
       </c>
@@ -4006,11 +4006,11 @@
       <c r="F154" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G154" s="54"/>
+      <c r="G154" s="48"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="48"/>
-      <c r="B155" s="66"/>
+      <c r="A155" s="51"/>
+      <c r="B155" s="45"/>
       <c r="C155" s="9" t="s">
         <v>56</v>
       </c>
@@ -4023,11 +4023,11 @@
       <c r="F155" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G155" s="54"/>
+      <c r="G155" s="48"/>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="48"/>
-      <c r="B156" s="66"/>
+      <c r="A156" s="51"/>
+      <c r="B156" s="45"/>
       <c r="C156" s="9" t="s">
         <v>16</v>
       </c>
@@ -4040,11 +4040,11 @@
       <c r="F156" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G156" s="54"/>
+      <c r="G156" s="48"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="48"/>
-      <c r="B157" s="66"/>
+      <c r="A157" s="51"/>
+      <c r="B157" s="45"/>
       <c r="C157" s="9" t="s">
         <v>17</v>
       </c>
@@ -4057,11 +4057,11 @@
       <c r="F157" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G157" s="54"/>
+      <c r="G157" s="48"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="48"/>
-      <c r="B158" s="66"/>
+      <c r="A158" s="51"/>
+      <c r="B158" s="45"/>
       <c r="C158" s="9" t="s">
         <v>57</v>
       </c>
@@ -4074,11 +4074,11 @@
       <c r="F158" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G158" s="54"/>
+      <c r="G158" s="48"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="48"/>
-      <c r="B159" s="66"/>
+      <c r="A159" s="51"/>
+      <c r="B159" s="45"/>
       <c r="C159" s="9" t="s">
         <v>20</v>
       </c>
@@ -4091,11 +4091,11 @@
       <c r="F159" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G159" s="54"/>
+      <c r="G159" s="48"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="48"/>
-      <c r="B160" s="66"/>
+      <c r="A160" s="51"/>
+      <c r="B160" s="45"/>
       <c r="C160" s="9" t="s">
         <v>21</v>
       </c>
@@ -4108,11 +4108,11 @@
       <c r="F160" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G160" s="54"/>
+      <c r="G160" s="48"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A161" s="48"/>
-      <c r="B161" s="66"/>
+      <c r="A161" s="51"/>
+      <c r="B161" s="45"/>
       <c r="C161" s="9" t="s">
         <v>22</v>
       </c>
@@ -4125,11 +4125,11 @@
       <c r="F161" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G161" s="54"/>
+      <c r="G161" s="48"/>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="49"/>
-      <c r="B162" s="67"/>
+      <c r="A162" s="52"/>
+      <c r="B162" s="46"/>
       <c r="C162" s="11" t="s">
         <v>23</v>
       </c>
@@ -4142,13 +4142,13 @@
       <c r="F162" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G162" s="55"/>
+      <c r="G162" s="49"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" s="56">
+      <c r="A163" s="41">
         <v>11</v>
       </c>
-      <c r="B163" s="65" t="s">
+      <c r="B163" s="44" t="s">
         <v>58</v>
       </c>
       <c r="C163" s="7" t="s">
@@ -4163,13 +4163,13 @@
       <c r="F163" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G163" s="53" t="s">
+      <c r="G163" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" s="57"/>
-      <c r="B164" s="66"/>
+      <c r="A164" s="42"/>
+      <c r="B164" s="45"/>
       <c r="C164" s="9" t="s">
         <v>5</v>
       </c>
@@ -4182,11 +4182,11 @@
       <c r="F164" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G164" s="54"/>
+      <c r="G164" s="48"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" s="57"/>
-      <c r="B165" s="66"/>
+      <c r="A165" s="42"/>
+      <c r="B165" s="45"/>
       <c r="C165" s="9" t="s">
         <v>8</v>
       </c>
@@ -4199,11 +4199,11 @@
       <c r="F165" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G165" s="54"/>
+      <c r="G165" s="48"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" s="57"/>
-      <c r="B166" s="66"/>
+      <c r="A166" s="42"/>
+      <c r="B166" s="45"/>
       <c r="C166" s="9" t="s">
         <v>10</v>
       </c>
@@ -4216,11 +4216,11 @@
       <c r="F166" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G166" s="54"/>
+      <c r="G166" s="48"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A167" s="57"/>
-      <c r="B167" s="66"/>
+      <c r="A167" s="42"/>
+      <c r="B167" s="45"/>
       <c r="C167" s="9" t="s">
         <v>11</v>
       </c>
@@ -4233,11 +4233,11 @@
       <c r="F167" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G167" s="54"/>
+      <c r="G167" s="48"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" s="57"/>
-      <c r="B168" s="66"/>
+      <c r="A168" s="42"/>
+      <c r="B168" s="45"/>
       <c r="C168" s="9" t="s">
         <v>13</v>
       </c>
@@ -4250,11 +4250,11 @@
       <c r="F168" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G168" s="54"/>
+      <c r="G168" s="48"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A169" s="57"/>
-      <c r="B169" s="66"/>
+      <c r="A169" s="42"/>
+      <c r="B169" s="45"/>
       <c r="C169" s="9" t="s">
         <v>56</v>
       </c>
@@ -4267,11 +4267,11 @@
       <c r="F169" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G169" s="54"/>
+      <c r="G169" s="48"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A170" s="57"/>
-      <c r="B170" s="66"/>
+      <c r="A170" s="42"/>
+      <c r="B170" s="45"/>
       <c r="C170" s="9" t="s">
         <v>16</v>
       </c>
@@ -4284,11 +4284,11 @@
       <c r="F170" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G170" s="54"/>
+      <c r="G170" s="48"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" s="57"/>
-      <c r="B171" s="66"/>
+      <c r="A171" s="42"/>
+      <c r="B171" s="45"/>
       <c r="C171" s="9" t="s">
         <v>17</v>
       </c>
@@ -4301,11 +4301,11 @@
       <c r="F171" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G171" s="54"/>
+      <c r="G171" s="48"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A172" s="57"/>
-      <c r="B172" s="66"/>
+      <c r="A172" s="42"/>
+      <c r="B172" s="45"/>
       <c r="C172" s="9" t="s">
         <v>57</v>
       </c>
@@ -4318,11 +4318,11 @@
       <c r="F172" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G172" s="54"/>
+      <c r="G172" s="48"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" s="57"/>
-      <c r="B173" s="66"/>
+      <c r="A173" s="42"/>
+      <c r="B173" s="45"/>
       <c r="C173" s="9" t="s">
         <v>20</v>
       </c>
@@ -4335,11 +4335,11 @@
       <c r="F173" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G173" s="54"/>
+      <c r="G173" s="48"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" s="57"/>
-      <c r="B174" s="66"/>
+      <c r="A174" s="42"/>
+      <c r="B174" s="45"/>
       <c r="C174" s="9" t="s">
         <v>21</v>
       </c>
@@ -4352,11 +4352,11 @@
       <c r="F174" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G174" s="54"/>
+      <c r="G174" s="48"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" s="57"/>
-      <c r="B175" s="66"/>
+      <c r="A175" s="42"/>
+      <c r="B175" s="45"/>
       <c r="C175" s="9" t="s">
         <v>22</v>
       </c>
@@ -4369,11 +4369,11 @@
       <c r="F175" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G175" s="54"/>
+      <c r="G175" s="48"/>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="58"/>
-      <c r="B176" s="67"/>
+      <c r="A176" s="43"/>
+      <c r="B176" s="46"/>
       <c r="C176" s="11" t="s">
         <v>23</v>
       </c>
@@ -4386,13 +4386,13 @@
       <c r="F176" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G176" s="55"/>
+      <c r="G176" s="49"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="47">
+      <c r="A177" s="50">
         <v>12</v>
       </c>
-      <c r="B177" s="65" t="s">
+      <c r="B177" s="44" t="s">
         <v>59</v>
       </c>
       <c r="C177" s="7" t="s">
@@ -4407,13 +4407,13 @@
       <c r="F177" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G177" s="53" t="s">
+      <c r="G177" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="48"/>
-      <c r="B178" s="66"/>
+      <c r="A178" s="51"/>
+      <c r="B178" s="45"/>
       <c r="C178" s="9" t="s">
         <v>27</v>
       </c>
@@ -4426,11 +4426,11 @@
       <c r="F178" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G178" s="54"/>
+      <c r="G178" s="48"/>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="48"/>
-      <c r="B179" s="66"/>
+      <c r="A179" s="51"/>
+      <c r="B179" s="45"/>
       <c r="C179" s="9" t="s">
         <v>28</v>
       </c>
@@ -4443,11 +4443,11 @@
       <c r="F179" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G179" s="54"/>
+      <c r="G179" s="48"/>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="48"/>
-      <c r="B180" s="66"/>
+      <c r="A180" s="51"/>
+      <c r="B180" s="45"/>
       <c r="C180" s="9" t="s">
         <v>29</v>
       </c>
@@ -4460,11 +4460,11 @@
       <c r="F180" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G180" s="54"/>
+      <c r="G180" s="48"/>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="48"/>
-      <c r="B181" s="66"/>
+      <c r="A181" s="51"/>
+      <c r="B181" s="45"/>
       <c r="C181" s="9" t="s">
         <v>30</v>
       </c>
@@ -4477,11 +4477,11 @@
       <c r="F181" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G181" s="54"/>
+      <c r="G181" s="48"/>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A182" s="48"/>
-      <c r="B182" s="66"/>
+      <c r="A182" s="51"/>
+      <c r="B182" s="45"/>
       <c r="C182" s="9" t="s">
         <v>31</v>
       </c>
@@ -4494,11 +4494,11 @@
       <c r="F182" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G182" s="54"/>
+      <c r="G182" s="48"/>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" s="48"/>
-      <c r="B183" s="66"/>
+      <c r="A183" s="51"/>
+      <c r="B183" s="45"/>
       <c r="C183" s="9" t="s">
         <v>60</v>
       </c>
@@ -4511,11 +4511,11 @@
       <c r="F183" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G183" s="54"/>
+      <c r="G183" s="48"/>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" s="48"/>
-      <c r="B184" s="66"/>
+      <c r="A184" s="51"/>
+      <c r="B184" s="45"/>
       <c r="C184" s="9" t="s">
         <v>61</v>
       </c>
@@ -4528,11 +4528,11 @@
       <c r="F184" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G184" s="54"/>
+      <c r="G184" s="48"/>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" s="48"/>
-      <c r="B185" s="66"/>
+      <c r="A185" s="51"/>
+      <c r="B185" s="45"/>
       <c r="C185" s="9" t="s">
         <v>56</v>
       </c>
@@ -4545,11 +4545,11 @@
       <c r="F185" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G185" s="54"/>
+      <c r="G185" s="48"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" s="48"/>
-      <c r="B186" s="66"/>
+      <c r="A186" s="51"/>
+      <c r="B186" s="45"/>
       <c r="C186" s="9" t="s">
         <v>34</v>
       </c>
@@ -4562,11 +4562,11 @@
       <c r="F186" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G186" s="54"/>
+      <c r="G186" s="48"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" s="48"/>
-      <c r="B187" s="66"/>
+      <c r="A187" s="51"/>
+      <c r="B187" s="45"/>
       <c r="C187" s="9" t="s">
         <v>16</v>
       </c>
@@ -4579,11 +4579,11 @@
       <c r="F187" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G187" s="54"/>
+      <c r="G187" s="48"/>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" s="48"/>
-      <c r="B188" s="66"/>
+      <c r="A188" s="51"/>
+      <c r="B188" s="45"/>
       <c r="C188" s="9" t="s">
         <v>17</v>
       </c>
@@ -4596,11 +4596,11 @@
       <c r="F188" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G188" s="54"/>
+      <c r="G188" s="48"/>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" s="48"/>
-      <c r="B189" s="66"/>
+      <c r="A189" s="51"/>
+      <c r="B189" s="45"/>
       <c r="C189" s="9" t="s">
         <v>57</v>
       </c>
@@ -4613,11 +4613,11 @@
       <c r="F189" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G189" s="54"/>
+      <c r="G189" s="48"/>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" s="48"/>
-      <c r="B190" s="66"/>
+      <c r="A190" s="51"/>
+      <c r="B190" s="45"/>
       <c r="C190" s="9" t="s">
         <v>20</v>
       </c>
@@ -4630,11 +4630,11 @@
       <c r="F190" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G190" s="54"/>
+      <c r="G190" s="48"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" s="48"/>
-      <c r="B191" s="66"/>
+      <c r="A191" s="51"/>
+      <c r="B191" s="45"/>
       <c r="C191" s="9" t="s">
         <v>21</v>
       </c>
@@ -4647,11 +4647,11 @@
       <c r="F191" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G191" s="54"/>
+      <c r="G191" s="48"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" s="48"/>
-      <c r="B192" s="66"/>
+      <c r="A192" s="51"/>
+      <c r="B192" s="45"/>
       <c r="C192" s="9" t="s">
         <v>22</v>
       </c>
@@ -4664,11 +4664,11 @@
       <c r="F192" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G192" s="54"/>
+      <c r="G192" s="48"/>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="49"/>
-      <c r="B193" s="67"/>
+      <c r="A193" s="52"/>
+      <c r="B193" s="46"/>
       <c r="C193" s="11" t="s">
         <v>23</v>
       </c>
@@ -4681,13 +4681,13 @@
       <c r="F193" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G193" s="55"/>
+      <c r="G193" s="49"/>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A194" s="47">
+      <c r="A194" s="50">
         <v>13</v>
       </c>
-      <c r="B194" s="65" t="s">
+      <c r="B194" s="44" t="s">
         <v>62</v>
       </c>
       <c r="C194" s="7" t="s">
@@ -4702,13 +4702,13 @@
       <c r="F194" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G194" s="53" t="s">
+      <c r="G194" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A195" s="48"/>
-      <c r="B195" s="66"/>
+      <c r="A195" s="51"/>
+      <c r="B195" s="45"/>
       <c r="C195" s="9" t="s">
         <v>27</v>
       </c>
@@ -4721,11 +4721,11 @@
       <c r="F195" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G195" s="54"/>
+      <c r="G195" s="48"/>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A196" s="48"/>
-      <c r="B196" s="66"/>
+      <c r="A196" s="51"/>
+      <c r="B196" s="45"/>
       <c r="C196" s="9" t="s">
         <v>28</v>
       </c>
@@ -4738,11 +4738,11 @@
       <c r="F196" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G196" s="54"/>
+      <c r="G196" s="48"/>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" s="48"/>
-      <c r="B197" s="66"/>
+      <c r="A197" s="51"/>
+      <c r="B197" s="45"/>
       <c r="C197" s="9" t="s">
         <v>29</v>
       </c>
@@ -4755,11 +4755,11 @@
       <c r="F197" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G197" s="54"/>
+      <c r="G197" s="48"/>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" s="48"/>
-      <c r="B198" s="66"/>
+      <c r="A198" s="51"/>
+      <c r="B198" s="45"/>
       <c r="C198" s="9" t="s">
         <v>30</v>
       </c>
@@ -4772,11 +4772,11 @@
       <c r="F198" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G198" s="54"/>
+      <c r="G198" s="48"/>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A199" s="48"/>
-      <c r="B199" s="66"/>
+      <c r="A199" s="51"/>
+      <c r="B199" s="45"/>
       <c r="C199" s="9" t="s">
         <v>31</v>
       </c>
@@ -4789,11 +4789,11 @@
       <c r="F199" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G199" s="54"/>
+      <c r="G199" s="48"/>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" s="48"/>
-      <c r="B200" s="66"/>
+      <c r="A200" s="51"/>
+      <c r="B200" s="45"/>
       <c r="C200" s="9" t="s">
         <v>60</v>
       </c>
@@ -4806,11 +4806,11 @@
       <c r="F200" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G200" s="54"/>
+      <c r="G200" s="48"/>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A201" s="48"/>
-      <c r="B201" s="66"/>
+      <c r="A201" s="51"/>
+      <c r="B201" s="45"/>
       <c r="C201" s="9" t="s">
         <v>61</v>
       </c>
@@ -4823,11 +4823,11 @@
       <c r="F201" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G201" s="54"/>
+      <c r="G201" s="48"/>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A202" s="48"/>
-      <c r="B202" s="66"/>
+      <c r="A202" s="51"/>
+      <c r="B202" s="45"/>
       <c r="C202" s="9" t="s">
         <v>56</v>
       </c>
@@ -4840,11 +4840,11 @@
       <c r="F202" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G202" s="54"/>
+      <c r="G202" s="48"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" s="48"/>
-      <c r="B203" s="66"/>
+      <c r="A203" s="51"/>
+      <c r="B203" s="45"/>
       <c r="C203" s="9" t="s">
         <v>34</v>
       </c>
@@ -4857,11 +4857,11 @@
       <c r="F203" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G203" s="54"/>
+      <c r="G203" s="48"/>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" s="48"/>
-      <c r="B204" s="66"/>
+      <c r="A204" s="51"/>
+      <c r="B204" s="45"/>
       <c r="C204" s="9" t="s">
         <v>16</v>
       </c>
@@ -4874,11 +4874,11 @@
       <c r="F204" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G204" s="54"/>
+      <c r="G204" s="48"/>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A205" s="48"/>
-      <c r="B205" s="66"/>
+      <c r="A205" s="51"/>
+      <c r="B205" s="45"/>
       <c r="C205" s="9" t="s">
         <v>17</v>
       </c>
@@ -4891,11 +4891,11 @@
       <c r="F205" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G205" s="54"/>
+      <c r="G205" s="48"/>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A206" s="48"/>
-      <c r="B206" s="66"/>
+      <c r="A206" s="51"/>
+      <c r="B206" s="45"/>
       <c r="C206" s="9" t="s">
         <v>57</v>
       </c>
@@ -4908,11 +4908,11 @@
       <c r="F206" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G206" s="54"/>
+      <c r="G206" s="48"/>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" s="48"/>
-      <c r="B207" s="66"/>
+      <c r="A207" s="51"/>
+      <c r="B207" s="45"/>
       <c r="C207" s="9" t="s">
         <v>20</v>
       </c>
@@ -4925,11 +4925,11 @@
       <c r="F207" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G207" s="54"/>
+      <c r="G207" s="48"/>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" s="48"/>
-      <c r="B208" s="66"/>
+      <c r="A208" s="51"/>
+      <c r="B208" s="45"/>
       <c r="C208" s="9" t="s">
         <v>21</v>
       </c>
@@ -4942,11 +4942,11 @@
       <c r="F208" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G208" s="54"/>
+      <c r="G208" s="48"/>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" s="48"/>
-      <c r="B209" s="66"/>
+      <c r="A209" s="51"/>
+      <c r="B209" s="45"/>
       <c r="C209" s="9" t="s">
         <v>22</v>
       </c>
@@ -4959,11 +4959,11 @@
       <c r="F209" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G209" s="54"/>
+      <c r="G209" s="48"/>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="49"/>
-      <c r="B210" s="67"/>
+      <c r="A210" s="52"/>
+      <c r="B210" s="46"/>
       <c r="C210" s="11" t="s">
         <v>23</v>
       </c>
@@ -4976,13 +4976,13 @@
       <c r="F210" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G210" s="55"/>
+      <c r="G210" s="49"/>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A211" s="47">
+      <c r="A211" s="50">
         <v>14</v>
       </c>
-      <c r="B211" s="50" t="s">
+      <c r="B211" s="53" t="s">
         <v>63</v>
       </c>
       <c r="C211" s="7" t="s">
@@ -4997,13 +4997,13 @@
       <c r="F211" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G211" s="53" t="s">
+      <c r="G211" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A212" s="48"/>
-      <c r="B212" s="51"/>
+      <c r="A212" s="51"/>
+      <c r="B212" s="54"/>
       <c r="C212" s="9" t="s">
         <v>37</v>
       </c>
@@ -5016,11 +5016,11 @@
       <c r="F212" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G212" s="54"/>
+      <c r="G212" s="48"/>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A213" s="48"/>
-      <c r="B213" s="51"/>
+      <c r="A213" s="51"/>
+      <c r="B213" s="54"/>
       <c r="C213" s="9" t="s">
         <v>28</v>
       </c>
@@ -5033,11 +5033,11 @@
       <c r="F213" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G213" s="54"/>
+      <c r="G213" s="48"/>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A214" s="48"/>
-      <c r="B214" s="51"/>
+      <c r="A214" s="51"/>
+      <c r="B214" s="54"/>
       <c r="C214" s="9" t="s">
         <v>29</v>
       </c>
@@ -5050,11 +5050,11 @@
       <c r="F214" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G214" s="54"/>
+      <c r="G214" s="48"/>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A215" s="48"/>
-      <c r="B215" s="51"/>
+      <c r="A215" s="51"/>
+      <c r="B215" s="54"/>
       <c r="C215" s="9" t="s">
         <v>30</v>
       </c>
@@ -5067,11 +5067,11 @@
       <c r="F215" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G215" s="54"/>
+      <c r="G215" s="48"/>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A216" s="48"/>
-      <c r="B216" s="51"/>
+      <c r="A216" s="51"/>
+      <c r="B216" s="54"/>
       <c r="C216" s="9" t="s">
         <v>31</v>
       </c>
@@ -5084,11 +5084,11 @@
       <c r="F216" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G216" s="54"/>
+      <c r="G216" s="48"/>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A217" s="48"/>
-      <c r="B217" s="51"/>
+      <c r="A217" s="51"/>
+      <c r="B217" s="54"/>
       <c r="C217" s="9" t="s">
         <v>60</v>
       </c>
@@ -5101,11 +5101,11 @@
       <c r="F217" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G217" s="54"/>
+      <c r="G217" s="48"/>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A218" s="48"/>
-      <c r="B218" s="51"/>
+      <c r="A218" s="51"/>
+      <c r="B218" s="54"/>
       <c r="C218" s="9" t="s">
         <v>61</v>
       </c>
@@ -5118,11 +5118,11 @@
       <c r="F218" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G218" s="54"/>
+      <c r="G218" s="48"/>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A219" s="48"/>
-      <c r="B219" s="51"/>
+      <c r="A219" s="51"/>
+      <c r="B219" s="54"/>
       <c r="C219" s="9" t="s">
         <v>56</v>
       </c>
@@ -5135,11 +5135,11 @@
       <c r="F219" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G219" s="54"/>
+      <c r="G219" s="48"/>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A220" s="48"/>
-      <c r="B220" s="51"/>
+      <c r="A220" s="51"/>
+      <c r="B220" s="54"/>
       <c r="C220" s="9" t="s">
         <v>34</v>
       </c>
@@ -5152,11 +5152,11 @@
       <c r="F220" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G220" s="54"/>
+      <c r="G220" s="48"/>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A221" s="48"/>
-      <c r="B221" s="51"/>
+      <c r="A221" s="51"/>
+      <c r="B221" s="54"/>
       <c r="C221" s="9" t="s">
         <v>16</v>
       </c>
@@ -5169,11 +5169,11 @@
       <c r="F221" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G221" s="54"/>
+      <c r="G221" s="48"/>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A222" s="48"/>
-      <c r="B222" s="51"/>
+      <c r="A222" s="51"/>
+      <c r="B222" s="54"/>
       <c r="C222" s="9" t="s">
         <v>17</v>
       </c>
@@ -5186,11 +5186,11 @@
       <c r="F222" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G222" s="54"/>
+      <c r="G222" s="48"/>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A223" s="48"/>
-      <c r="B223" s="51"/>
+      <c r="A223" s="51"/>
+      <c r="B223" s="54"/>
       <c r="C223" s="9" t="s">
         <v>57</v>
       </c>
@@ -5203,11 +5203,11 @@
       <c r="F223" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G223" s="54"/>
+      <c r="G223" s="48"/>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A224" s="48"/>
-      <c r="B224" s="51"/>
+      <c r="A224" s="51"/>
+      <c r="B224" s="54"/>
       <c r="C224" s="9" t="s">
         <v>20</v>
       </c>
@@ -5220,11 +5220,11 @@
       <c r="F224" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G224" s="54"/>
+      <c r="G224" s="48"/>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A225" s="48"/>
-      <c r="B225" s="51"/>
+      <c r="A225" s="51"/>
+      <c r="B225" s="54"/>
       <c r="C225" s="9" t="s">
         <v>21</v>
       </c>
@@ -5237,11 +5237,11 @@
       <c r="F225" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G225" s="54"/>
+      <c r="G225" s="48"/>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A226" s="48"/>
-      <c r="B226" s="51"/>
+      <c r="A226" s="51"/>
+      <c r="B226" s="54"/>
       <c r="C226" s="9" t="s">
         <v>22</v>
       </c>
@@ -5254,11 +5254,11 @@
       <c r="F226" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G226" s="54"/>
+      <c r="G226" s="48"/>
     </row>
     <row r="227" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="49"/>
-      <c r="B227" s="52"/>
+      <c r="A227" s="52"/>
+      <c r="B227" s="55"/>
       <c r="C227" s="11" t="s">
         <v>23</v>
       </c>
@@ -5271,13 +5271,13 @@
       <c r="F227" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G227" s="55"/>
+      <c r="G227" s="49"/>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A228" s="47">
-        <v>15</v>
-      </c>
-      <c r="B228" s="50" t="s">
+      <c r="A228" s="50">
+        <v>15</v>
+      </c>
+      <c r="B228" s="53" t="s">
         <v>64</v>
       </c>
       <c r="C228" s="7" t="s">
@@ -5292,13 +5292,13 @@
       <c r="F228" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G228" s="53" t="s">
+      <c r="G228" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A229" s="48"/>
-      <c r="B229" s="51"/>
+      <c r="A229" s="51"/>
+      <c r="B229" s="54"/>
       <c r="C229" s="9" t="s">
         <v>37</v>
       </c>
@@ -5311,11 +5311,11 @@
       <c r="F229" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G229" s="54"/>
+      <c r="G229" s="48"/>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A230" s="48"/>
-      <c r="B230" s="51"/>
+      <c r="A230" s="51"/>
+      <c r="B230" s="54"/>
       <c r="C230" s="9" t="s">
         <v>28</v>
       </c>
@@ -5328,11 +5328,11 @@
       <c r="F230" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G230" s="54"/>
+      <c r="G230" s="48"/>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A231" s="48"/>
-      <c r="B231" s="51"/>
+      <c r="A231" s="51"/>
+      <c r="B231" s="54"/>
       <c r="C231" s="9" t="s">
         <v>29</v>
       </c>
@@ -5345,11 +5345,11 @@
       <c r="F231" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G231" s="54"/>
+      <c r="G231" s="48"/>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A232" s="48"/>
-      <c r="B232" s="51"/>
+      <c r="A232" s="51"/>
+      <c r="B232" s="54"/>
       <c r="C232" s="9" t="s">
         <v>30</v>
       </c>
@@ -5362,11 +5362,11 @@
       <c r="F232" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G232" s="54"/>
+      <c r="G232" s="48"/>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A233" s="48"/>
-      <c r="B233" s="51"/>
+      <c r="A233" s="51"/>
+      <c r="B233" s="54"/>
       <c r="C233" s="9" t="s">
         <v>31</v>
       </c>
@@ -5379,11 +5379,11 @@
       <c r="F233" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G233" s="54"/>
+      <c r="G233" s="48"/>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A234" s="48"/>
-      <c r="B234" s="51"/>
+      <c r="A234" s="51"/>
+      <c r="B234" s="54"/>
       <c r="C234" s="9" t="s">
         <v>60</v>
       </c>
@@ -5396,11 +5396,11 @@
       <c r="F234" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G234" s="54"/>
+      <c r="G234" s="48"/>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A235" s="48"/>
-      <c r="B235" s="51"/>
+      <c r="A235" s="51"/>
+      <c r="B235" s="54"/>
       <c r="C235" s="9" t="s">
         <v>61</v>
       </c>
@@ -5413,11 +5413,11 @@
       <c r="F235" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G235" s="54"/>
+      <c r="G235" s="48"/>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A236" s="48"/>
-      <c r="B236" s="51"/>
+      <c r="A236" s="51"/>
+      <c r="B236" s="54"/>
       <c r="C236" s="9" t="s">
         <v>56</v>
       </c>
@@ -5430,11 +5430,11 @@
       <c r="F236" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G236" s="54"/>
+      <c r="G236" s="48"/>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A237" s="48"/>
-      <c r="B237" s="51"/>
+      <c r="A237" s="51"/>
+      <c r="B237" s="54"/>
       <c r="C237" s="9" t="s">
         <v>34</v>
       </c>
@@ -5447,11 +5447,11 @@
       <c r="F237" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G237" s="54"/>
+      <c r="G237" s="48"/>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A238" s="48"/>
-      <c r="B238" s="51"/>
+      <c r="A238" s="51"/>
+      <c r="B238" s="54"/>
       <c r="C238" s="9" t="s">
         <v>16</v>
       </c>
@@ -5464,11 +5464,11 @@
       <c r="F238" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G238" s="54"/>
+      <c r="G238" s="48"/>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A239" s="48"/>
-      <c r="B239" s="51"/>
+      <c r="A239" s="51"/>
+      <c r="B239" s="54"/>
       <c r="C239" s="9" t="s">
         <v>17</v>
       </c>
@@ -5481,11 +5481,11 @@
       <c r="F239" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G239" s="54"/>
+      <c r="G239" s="48"/>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A240" s="48"/>
-      <c r="B240" s="51"/>
+      <c r="A240" s="51"/>
+      <c r="B240" s="54"/>
       <c r="C240" s="9" t="s">
         <v>57</v>
       </c>
@@ -5498,11 +5498,11 @@
       <c r="F240" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G240" s="54"/>
+      <c r="G240" s="48"/>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A241" s="48"/>
-      <c r="B241" s="51"/>
+      <c r="A241" s="51"/>
+      <c r="B241" s="54"/>
       <c r="C241" s="9" t="s">
         <v>20</v>
       </c>
@@ -5515,11 +5515,11 @@
       <c r="F241" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G241" s="54"/>
+      <c r="G241" s="48"/>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A242" s="48"/>
-      <c r="B242" s="51"/>
+      <c r="A242" s="51"/>
+      <c r="B242" s="54"/>
       <c r="C242" s="9" t="s">
         <v>21</v>
       </c>
@@ -5532,11 +5532,11 @@
       <c r="F242" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G242" s="54"/>
+      <c r="G242" s="48"/>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" s="48"/>
-      <c r="B243" s="51"/>
+      <c r="A243" s="51"/>
+      <c r="B243" s="54"/>
       <c r="C243" s="9" t="s">
         <v>22</v>
       </c>
@@ -5549,11 +5549,11 @@
       <c r="F243" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G243" s="54"/>
+      <c r="G243" s="48"/>
     </row>
     <row r="244" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="49"/>
-      <c r="B244" s="52"/>
+      <c r="A244" s="52"/>
+      <c r="B244" s="55"/>
       <c r="C244" s="11" t="s">
         <v>23</v>
       </c>
@@ -5566,13 +5566,13 @@
       <c r="F244" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G244" s="55"/>
+      <c r="G244" s="49"/>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A245" s="47">
+      <c r="A245" s="50">
         <v>16</v>
       </c>
-      <c r="B245" s="62" t="s">
+      <c r="B245" s="56" t="s">
         <v>65</v>
       </c>
       <c r="C245" s="7" t="s">
@@ -5587,13 +5587,13 @@
       <c r="F245" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G245" s="53" t="s">
+      <c r="G245" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" s="48"/>
-      <c r="B246" s="63"/>
+      <c r="A246" s="51"/>
+      <c r="B246" s="57"/>
       <c r="C246" s="9" t="s">
         <v>41</v>
       </c>
@@ -5606,11 +5606,11 @@
       <c r="F246" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G246" s="54"/>
+      <c r="G246" s="48"/>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" s="48"/>
-      <c r="B247" s="63"/>
+      <c r="A247" s="51"/>
+      <c r="B247" s="57"/>
       <c r="C247" s="9" t="s">
         <v>42</v>
       </c>
@@ -5623,11 +5623,11 @@
       <c r="F247" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G247" s="54"/>
+      <c r="G247" s="48"/>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" s="48"/>
-      <c r="B248" s="63"/>
+      <c r="A248" s="51"/>
+      <c r="B248" s="57"/>
       <c r="C248" s="9" t="s">
         <v>43</v>
       </c>
@@ -5640,11 +5640,11 @@
       <c r="F248" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G248" s="54"/>
+      <c r="G248" s="48"/>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" s="48"/>
-      <c r="B249" s="63"/>
+      <c r="A249" s="51"/>
+      <c r="B249" s="57"/>
       <c r="C249" s="9" t="s">
         <v>44</v>
       </c>
@@ -5657,11 +5657,11 @@
       <c r="F249" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G249" s="54"/>
+      <c r="G249" s="48"/>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" s="48"/>
-      <c r="B250" s="63"/>
+      <c r="A250" s="51"/>
+      <c r="B250" s="57"/>
       <c r="C250" s="9" t="s">
         <v>13</v>
       </c>
@@ -5674,11 +5674,11 @@
       <c r="F250" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G250" s="54"/>
+      <c r="G250" s="48"/>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" s="48"/>
-      <c r="B251" s="63"/>
+      <c r="A251" s="51"/>
+      <c r="B251" s="57"/>
       <c r="C251" s="9" t="s">
         <v>61</v>
       </c>
@@ -5691,11 +5691,11 @@
       <c r="F251" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G251" s="54"/>
+      <c r="G251" s="48"/>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A252" s="48"/>
-      <c r="B252" s="63"/>
+      <c r="A252" s="51"/>
+      <c r="B252" s="57"/>
       <c r="C252" s="9" t="s">
         <v>56</v>
       </c>
@@ -5708,11 +5708,11 @@
       <c r="F252" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G252" s="54"/>
+      <c r="G252" s="48"/>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A253" s="48"/>
-      <c r="B253" s="63"/>
+      <c r="A253" s="51"/>
+      <c r="B253" s="57"/>
       <c r="C253" s="9" t="s">
         <v>34</v>
       </c>
@@ -5725,11 +5725,11 @@
       <c r="F253" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G253" s="54"/>
+      <c r="G253" s="48"/>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A254" s="48"/>
-      <c r="B254" s="63"/>
+      <c r="A254" s="51"/>
+      <c r="B254" s="57"/>
       <c r="C254" s="9" t="s">
         <v>16</v>
       </c>
@@ -5742,11 +5742,11 @@
       <c r="F254" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G254" s="54"/>
+      <c r="G254" s="48"/>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A255" s="48"/>
-      <c r="B255" s="63"/>
+      <c r="A255" s="51"/>
+      <c r="B255" s="57"/>
       <c r="C255" s="9" t="s">
         <v>60</v>
       </c>
@@ -5759,11 +5759,11 @@
       <c r="F255" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G255" s="54"/>
+      <c r="G255" s="48"/>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A256" s="48"/>
-      <c r="B256" s="63"/>
+      <c r="A256" s="51"/>
+      <c r="B256" s="57"/>
       <c r="C256" s="9" t="s">
         <v>17</v>
       </c>
@@ -5776,11 +5776,11 @@
       <c r="F256" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G256" s="54"/>
+      <c r="G256" s="48"/>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A257" s="48"/>
-      <c r="B257" s="63"/>
+      <c r="A257" s="51"/>
+      <c r="B257" s="57"/>
       <c r="C257" s="9" t="s">
         <v>57</v>
       </c>
@@ -5793,11 +5793,11 @@
       <c r="F257" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G257" s="54"/>
+      <c r="G257" s="48"/>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A258" s="48"/>
-      <c r="B258" s="63"/>
+      <c r="A258" s="51"/>
+      <c r="B258" s="57"/>
       <c r="C258" s="9" t="s">
         <v>20</v>
       </c>
@@ -5810,11 +5810,11 @@
       <c r="F258" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G258" s="54"/>
+      <c r="G258" s="48"/>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A259" s="48"/>
-      <c r="B259" s="63"/>
+      <c r="A259" s="51"/>
+      <c r="B259" s="57"/>
       <c r="C259" s="9" t="s">
         <v>21</v>
       </c>
@@ -5827,11 +5827,11 @@
       <c r="F259" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G259" s="54"/>
+      <c r="G259" s="48"/>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A260" s="48"/>
-      <c r="B260" s="63"/>
+      <c r="A260" s="51"/>
+      <c r="B260" s="57"/>
       <c r="C260" s="9" t="s">
         <v>22</v>
       </c>
@@ -5844,11 +5844,11 @@
       <c r="F260" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G260" s="54"/>
+      <c r="G260" s="48"/>
     </row>
     <row r="261" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A261" s="49"/>
-      <c r="B261" s="64"/>
+      <c r="A261" s="52"/>
+      <c r="B261" s="58"/>
       <c r="C261" s="11" t="s">
         <v>23</v>
       </c>
@@ -5861,13 +5861,13 @@
       <c r="F261" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G261" s="55"/>
+      <c r="G261" s="49"/>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A262" s="47">
+      <c r="A262" s="50">
         <v>17</v>
       </c>
-      <c r="B262" s="50" t="s">
+      <c r="B262" s="53" t="s">
         <v>66</v>
       </c>
       <c r="C262" s="7" t="s">
@@ -5882,13 +5882,13 @@
       <c r="F262" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G262" s="53" t="s">
+      <c r="G262" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A263" s="48"/>
-      <c r="B263" s="51"/>
+      <c r="A263" s="51"/>
+      <c r="B263" s="54"/>
       <c r="C263" s="9" t="s">
         <v>5</v>
       </c>
@@ -5901,11 +5901,11 @@
       <c r="F263" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G263" s="54"/>
+      <c r="G263" s="48"/>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A264" s="48"/>
-      <c r="B264" s="51"/>
+      <c r="A264" s="51"/>
+      <c r="B264" s="54"/>
       <c r="C264" s="9" t="s">
         <v>47</v>
       </c>
@@ -5918,11 +5918,11 @@
       <c r="F264" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G264" s="54"/>
+      <c r="G264" s="48"/>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A265" s="48"/>
-      <c r="B265" s="51"/>
+      <c r="A265" s="51"/>
+      <c r="B265" s="54"/>
       <c r="C265" s="9" t="s">
         <v>48</v>
       </c>
@@ -5935,11 +5935,11 @@
       <c r="F265" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G265" s="54"/>
+      <c r="G265" s="48"/>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A266" s="48"/>
-      <c r="B266" s="51"/>
+      <c r="A266" s="51"/>
+      <c r="B266" s="54"/>
       <c r="C266" s="9" t="s">
         <v>49</v>
       </c>
@@ -5952,11 +5952,11 @@
       <c r="F266" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G266" s="54"/>
+      <c r="G266" s="48"/>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A267" s="48"/>
-      <c r="B267" s="51"/>
+      <c r="A267" s="51"/>
+      <c r="B267" s="54"/>
       <c r="C267" s="9" t="s">
         <v>50</v>
       </c>
@@ -5969,11 +5969,11 @@
       <c r="F267" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G267" s="54"/>
+      <c r="G267" s="48"/>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A268" s="48"/>
-      <c r="B268" s="51"/>
+      <c r="A268" s="51"/>
+      <c r="B268" s="54"/>
       <c r="C268" s="9" t="s">
         <v>13</v>
       </c>
@@ -5986,11 +5986,11 @@
       <c r="F268" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G268" s="54"/>
+      <c r="G268" s="48"/>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A269" s="48"/>
-      <c r="B269" s="51"/>
+      <c r="A269" s="51"/>
+      <c r="B269" s="54"/>
       <c r="C269" s="9" t="s">
         <v>56</v>
       </c>
@@ -6003,11 +6003,11 @@
       <c r="F269" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G269" s="54"/>
+      <c r="G269" s="48"/>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A270" s="48"/>
-      <c r="B270" s="51"/>
+      <c r="A270" s="51"/>
+      <c r="B270" s="54"/>
       <c r="C270" s="9" t="s">
         <v>16</v>
       </c>
@@ -6020,11 +6020,11 @@
       <c r="F270" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G270" s="54"/>
+      <c r="G270" s="48"/>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A271" s="48"/>
-      <c r="B271" s="51"/>
+      <c r="A271" s="51"/>
+      <c r="B271" s="54"/>
       <c r="C271" s="9" t="s">
         <v>34</v>
       </c>
@@ -6037,11 +6037,11 @@
       <c r="F271" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G271" s="54"/>
+      <c r="G271" s="48"/>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A272" s="48"/>
-      <c r="B272" s="51"/>
+      <c r="A272" s="51"/>
+      <c r="B272" s="54"/>
       <c r="C272" s="9" t="s">
         <v>60</v>
       </c>
@@ -6054,11 +6054,11 @@
       <c r="F272" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G272" s="54"/>
+      <c r="G272" s="48"/>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A273" s="48"/>
-      <c r="B273" s="51"/>
+      <c r="A273" s="51"/>
+      <c r="B273" s="54"/>
       <c r="C273" s="9" t="s">
         <v>17</v>
       </c>
@@ -6071,11 +6071,11 @@
       <c r="F273" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G273" s="54"/>
+      <c r="G273" s="48"/>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A274" s="48"/>
-      <c r="B274" s="51"/>
+      <c r="A274" s="51"/>
+      <c r="B274" s="54"/>
       <c r="C274" s="9" t="s">
         <v>57</v>
       </c>
@@ -6088,11 +6088,11 @@
       <c r="F274" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G274" s="54"/>
+      <c r="G274" s="48"/>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A275" s="48"/>
-      <c r="B275" s="51"/>
+      <c r="A275" s="51"/>
+      <c r="B275" s="54"/>
       <c r="C275" s="9" t="s">
         <v>20</v>
       </c>
@@ -6105,11 +6105,11 @@
       <c r="F275" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G275" s="54"/>
+      <c r="G275" s="48"/>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A276" s="48"/>
-      <c r="B276" s="51"/>
+      <c r="A276" s="51"/>
+      <c r="B276" s="54"/>
       <c r="C276" s="9" t="s">
         <v>21</v>
       </c>
@@ -6122,11 +6122,11 @@
       <c r="F276" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G276" s="54"/>
+      <c r="G276" s="48"/>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" s="48"/>
-      <c r="B277" s="51"/>
+      <c r="A277" s="51"/>
+      <c r="B277" s="54"/>
       <c r="C277" s="9" t="s">
         <v>22</v>
       </c>
@@ -6139,11 +6139,11 @@
       <c r="F277" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G277" s="54"/>
+      <c r="G277" s="48"/>
     </row>
     <row r="278" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="49"/>
-      <c r="B278" s="52"/>
+      <c r="A278" s="52"/>
+      <c r="B278" s="55"/>
       <c r="C278" s="11" t="s">
         <v>23</v>
       </c>
@@ -6156,13 +6156,13 @@
       <c r="F278" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G278" s="55"/>
+      <c r="G278" s="49"/>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A279" s="56">
+      <c r="A279" s="41">
         <v>18</v>
       </c>
-      <c r="B279" s="59" t="s">
+      <c r="B279" s="67" t="s">
         <v>67</v>
       </c>
       <c r="C279" s="7" t="s">
@@ -6177,13 +6177,13 @@
       <c r="F279" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G279" s="53" t="s">
+      <c r="G279" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A280" s="57"/>
-      <c r="B280" s="60"/>
+      <c r="A280" s="42"/>
+      <c r="B280" s="68"/>
       <c r="C280" s="9" t="s">
         <v>52</v>
       </c>
@@ -6196,11 +6196,11 @@
       <c r="F280" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G280" s="54"/>
+      <c r="G280" s="48"/>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A281" s="57"/>
-      <c r="B281" s="60"/>
+      <c r="A281" s="42"/>
+      <c r="B281" s="68"/>
       <c r="C281" s="9" t="s">
         <v>53</v>
       </c>
@@ -6213,11 +6213,11 @@
       <c r="F281" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G281" s="54"/>
+      <c r="G281" s="48"/>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" s="57"/>
-      <c r="B282" s="60"/>
+      <c r="A282" s="42"/>
+      <c r="B282" s="68"/>
       <c r="C282" s="9" t="s">
         <v>47</v>
       </c>
@@ -6230,11 +6230,11 @@
       <c r="F282" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G282" s="54"/>
+      <c r="G282" s="48"/>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A283" s="57"/>
-      <c r="B283" s="60"/>
+      <c r="A283" s="42"/>
+      <c r="B283" s="68"/>
       <c r="C283" s="9" t="s">
         <v>48</v>
       </c>
@@ -6247,11 +6247,11 @@
       <c r="F283" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G283" s="54"/>
+      <c r="G283" s="48"/>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A284" s="57"/>
-      <c r="B284" s="60"/>
+      <c r="A284" s="42"/>
+      <c r="B284" s="68"/>
       <c r="C284" s="9" t="s">
         <v>49</v>
       </c>
@@ -6264,11 +6264,11 @@
       <c r="F284" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G284" s="54"/>
+      <c r="G284" s="48"/>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A285" s="57"/>
-      <c r="B285" s="60"/>
+      <c r="A285" s="42"/>
+      <c r="B285" s="68"/>
       <c r="C285" s="9" t="s">
         <v>50</v>
       </c>
@@ -6281,11 +6281,11 @@
       <c r="F285" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G285" s="54"/>
+      <c r="G285" s="48"/>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A286" s="57"/>
-      <c r="B286" s="60"/>
+      <c r="A286" s="42"/>
+      <c r="B286" s="68"/>
       <c r="C286" s="9" t="s">
         <v>13</v>
       </c>
@@ -6298,11 +6298,11 @@
       <c r="F286" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G286" s="54"/>
+      <c r="G286" s="48"/>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A287" s="57"/>
-      <c r="B287" s="60"/>
+      <c r="A287" s="42"/>
+      <c r="B287" s="68"/>
       <c r="C287" s="9" t="s">
         <v>56</v>
       </c>
@@ -6315,11 +6315,11 @@
       <c r="F287" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G287" s="54"/>
+      <c r="G287" s="48"/>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A288" s="57"/>
-      <c r="B288" s="60"/>
+      <c r="A288" s="42"/>
+      <c r="B288" s="68"/>
       <c r="C288" s="9" t="s">
         <v>16</v>
       </c>
@@ -6332,11 +6332,11 @@
       <c r="F288" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G288" s="54"/>
+      <c r="G288" s="48"/>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A289" s="57"/>
-      <c r="B289" s="60"/>
+      <c r="A289" s="42"/>
+      <c r="B289" s="68"/>
       <c r="C289" s="9" t="s">
         <v>60</v>
       </c>
@@ -6349,11 +6349,11 @@
       <c r="F289" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G289" s="54"/>
+      <c r="G289" s="48"/>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A290" s="57"/>
-      <c r="B290" s="60"/>
+      <c r="A290" s="42"/>
+      <c r="B290" s="68"/>
       <c r="C290" s="9" t="s">
         <v>17</v>
       </c>
@@ -6366,11 +6366,11 @@
       <c r="F290" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G290" s="54"/>
+      <c r="G290" s="48"/>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A291" s="57"/>
-      <c r="B291" s="60"/>
+      <c r="A291" s="42"/>
+      <c r="B291" s="68"/>
       <c r="C291" s="9" t="s">
         <v>57</v>
       </c>
@@ -6383,11 +6383,11 @@
       <c r="F291" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G291" s="54"/>
+      <c r="G291" s="48"/>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A292" s="57"/>
-      <c r="B292" s="60"/>
+      <c r="A292" s="42"/>
+      <c r="B292" s="68"/>
       <c r="C292" s="9" t="s">
         <v>20</v>
       </c>
@@ -6400,11 +6400,11 @@
       <c r="F292" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G292" s="54"/>
+      <c r="G292" s="48"/>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A293" s="57"/>
-      <c r="B293" s="60"/>
+      <c r="A293" s="42"/>
+      <c r="B293" s="68"/>
       <c r="C293" s="9" t="s">
         <v>21</v>
       </c>
@@ -6417,11 +6417,11 @@
       <c r="F293" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G293" s="54"/>
+      <c r="G293" s="48"/>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" s="57"/>
-      <c r="B294" s="60"/>
+      <c r="A294" s="42"/>
+      <c r="B294" s="68"/>
       <c r="C294" s="9" t="s">
         <v>22</v>
       </c>
@@ -6434,11 +6434,11 @@
       <c r="F294" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G294" s="54"/>
+      <c r="G294" s="48"/>
     </row>
     <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A295" s="58"/>
-      <c r="B295" s="61"/>
+      <c r="A295" s="43"/>
+      <c r="B295" s="69"/>
       <c r="C295" s="11" t="s">
         <v>23</v>
       </c>
@@ -6451,13 +6451,13 @@
       <c r="F295" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G295" s="55"/>
+      <c r="G295" s="49"/>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A296" s="29">
+      <c r="A296" s="59">
         <v>19</v>
       </c>
-      <c r="B296" s="44" t="s">
+      <c r="B296" s="61" t="s">
         <v>68</v>
       </c>
       <c r="C296" s="13" t="s">
@@ -6472,13 +6472,13 @@
       <c r="F296" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G296" s="45" t="s">
+      <c r="G296" s="63" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297" s="43"/>
-      <c r="B297" s="27"/>
+      <c r="A297" s="60"/>
+      <c r="B297" s="62"/>
       <c r="C297" s="13" t="s">
         <v>71</v>
       </c>
@@ -6491,11 +6491,11 @@
       <c r="F297" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G297" s="45"/>
+      <c r="G297" s="63"/>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298" s="43"/>
-      <c r="B298" s="27"/>
+      <c r="A298" s="60"/>
+      <c r="B298" s="62"/>
       <c r="C298" s="13" t="s">
         <v>72</v>
       </c>
@@ -6508,11 +6508,11 @@
       <c r="F298" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G298" s="45"/>
+      <c r="G298" s="63"/>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A299" s="43"/>
-      <c r="B299" s="27"/>
+      <c r="A299" s="60"/>
+      <c r="B299" s="62"/>
       <c r="C299" s="13" t="s">
         <v>74</v>
       </c>
@@ -6525,11 +6525,11 @@
       <c r="F299" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G299" s="45"/>
+      <c r="G299" s="63"/>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A300" s="43"/>
-      <c r="B300" s="27"/>
+      <c r="A300" s="60"/>
+      <c r="B300" s="62"/>
       <c r="C300" s="13" t="s">
         <v>75</v>
       </c>
@@ -6542,11 +6542,11 @@
       <c r="F300" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G300" s="45"/>
+      <c r="G300" s="63"/>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A301" s="43"/>
-      <c r="B301" s="27"/>
+      <c r="A301" s="60"/>
+      <c r="B301" s="62"/>
       <c r="C301" s="13" t="s">
         <v>41</v>
       </c>
@@ -6559,11 +6559,11 @@
       <c r="F301" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G301" s="45"/>
+      <c r="G301" s="63"/>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A302" s="43"/>
-      <c r="B302" s="27"/>
+      <c r="A302" s="60"/>
+      <c r="B302" s="62"/>
       <c r="C302" s="13" t="s">
         <v>53</v>
       </c>
@@ -6576,11 +6576,11 @@
       <c r="F302" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G302" s="45"/>
+      <c r="G302" s="63"/>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A303" s="43"/>
-      <c r="B303" s="27"/>
+      <c r="A303" s="60"/>
+      <c r="B303" s="62"/>
       <c r="C303" s="13" t="s">
         <v>43</v>
       </c>
@@ -6593,11 +6593,11 @@
       <c r="F303" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G303" s="45"/>
+      <c r="G303" s="63"/>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A304" s="43"/>
-      <c r="B304" s="27"/>
+      <c r="A304" s="60"/>
+      <c r="B304" s="62"/>
       <c r="C304" s="13" t="s">
         <v>13</v>
       </c>
@@ -6610,11 +6610,11 @@
       <c r="F304" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G304" s="45"/>
+      <c r="G304" s="63"/>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A305" s="43"/>
-      <c r="B305" s="27"/>
+      <c r="A305" s="60"/>
+      <c r="B305" s="62"/>
       <c r="C305" s="13" t="s">
         <v>17</v>
       </c>
@@ -6627,11 +6627,11 @@
       <c r="F305" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G305" s="45"/>
+      <c r="G305" s="63"/>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A306" s="43"/>
-      <c r="B306" s="27"/>
+      <c r="A306" s="60"/>
+      <c r="B306" s="62"/>
       <c r="C306" s="13" t="s">
         <v>16</v>
       </c>
@@ -6644,11 +6644,11 @@
       <c r="F306" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G306" s="45"/>
+      <c r="G306" s="63"/>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A307" s="43"/>
-      <c r="B307" s="27"/>
+      <c r="A307" s="60"/>
+      <c r="B307" s="62"/>
       <c r="C307" s="13" t="s">
         <v>32</v>
       </c>
@@ -6661,11 +6661,11 @@
       <c r="F307" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G307" s="45"/>
+      <c r="G307" s="63"/>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A308" s="43"/>
-      <c r="B308" s="27"/>
+      <c r="A308" s="60"/>
+      <c r="B308" s="62"/>
       <c r="C308" s="13" t="s">
         <v>76</v>
       </c>
@@ -6678,11 +6678,11 @@
       <c r="F308" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G308" s="45"/>
+      <c r="G308" s="63"/>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A309" s="43"/>
-      <c r="B309" s="27"/>
+      <c r="A309" s="60"/>
+      <c r="B309" s="62"/>
       <c r="C309" s="13" t="s">
         <v>18</v>
       </c>
@@ -6695,11 +6695,11 @@
       <c r="F309" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G309" s="45"/>
+      <c r="G309" s="63"/>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A310" s="43"/>
-      <c r="B310" s="27"/>
+      <c r="A310" s="60"/>
+      <c r="B310" s="62"/>
       <c r="C310" s="13" t="s">
         <v>21</v>
       </c>
@@ -6712,11 +6712,11 @@
       <c r="F310" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G310" s="45"/>
+      <c r="G310" s="63"/>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A311" s="43"/>
-      <c r="B311" s="27"/>
+      <c r="A311" s="60"/>
+      <c r="B311" s="62"/>
       <c r="C311" s="13" t="s">
         <v>20</v>
       </c>
@@ -6729,11 +6729,11 @@
       <c r="F311" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G311" s="45"/>
+      <c r="G311" s="63"/>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A312" s="43"/>
-      <c r="B312" s="27"/>
+      <c r="A312" s="60"/>
+      <c r="B312" s="62"/>
       <c r="C312" s="13" t="s">
         <v>22</v>
       </c>
@@ -6746,11 +6746,11 @@
       <c r="F312" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G312" s="45"/>
+      <c r="G312" s="63"/>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A313" s="43"/>
-      <c r="B313" s="29"/>
+      <c r="A313" s="60"/>
+      <c r="B313" s="59"/>
       <c r="C313" s="13" t="s">
         <v>23</v>
       </c>
@@ -6763,13 +6763,13 @@
       <c r="F313" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G313" s="46"/>
+      <c r="G313" s="64"/>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A314" s="26">
+      <c r="A314" s="65">
         <v>20</v>
       </c>
-      <c r="B314" s="28" t="s">
+      <c r="B314" s="66" t="s">
         <v>77</v>
       </c>
       <c r="C314" s="16" t="s">
@@ -6784,13 +6784,13 @@
       <c r="F314" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G314" s="26" t="s">
+      <c r="G314" s="65" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A315" s="27"/>
-      <c r="B315" s="27"/>
+      <c r="A315" s="62"/>
+      <c r="B315" s="62"/>
       <c r="C315" s="16" t="s">
         <v>71</v>
       </c>
@@ -6803,11 +6803,11 @@
       <c r="F315" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G315" s="27"/>
+      <c r="G315" s="62"/>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A316" s="27"/>
-      <c r="B316" s="27"/>
+      <c r="A316" s="62"/>
+      <c r="B316" s="62"/>
       <c r="C316" s="16" t="s">
         <v>72</v>
       </c>
@@ -6820,11 +6820,11 @@
       <c r="F316" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G316" s="27"/>
+      <c r="G316" s="62"/>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A317" s="27"/>
-      <c r="B317" s="27"/>
+      <c r="A317" s="62"/>
+      <c r="B317" s="62"/>
       <c r="C317" s="16" t="s">
         <v>74</v>
       </c>
@@ -6837,11 +6837,11 @@
       <c r="F317" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G317" s="27"/>
+      <c r="G317" s="62"/>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A318" s="27"/>
-      <c r="B318" s="27"/>
+      <c r="A318" s="62"/>
+      <c r="B318" s="62"/>
       <c r="C318" s="16" t="s">
         <v>75</v>
       </c>
@@ -6854,11 +6854,11 @@
       <c r="F318" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G318" s="27"/>
+      <c r="G318" s="62"/>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A319" s="27"/>
-      <c r="B319" s="27"/>
+      <c r="A319" s="62"/>
+      <c r="B319" s="62"/>
       <c r="C319" s="16" t="s">
         <v>41</v>
       </c>
@@ -6871,11 +6871,11 @@
       <c r="F319" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G319" s="27"/>
+      <c r="G319" s="62"/>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A320" s="27"/>
-      <c r="B320" s="27"/>
+      <c r="A320" s="62"/>
+      <c r="B320" s="62"/>
       <c r="C320" s="16" t="s">
         <v>53</v>
       </c>
@@ -6888,11 +6888,11 @@
       <c r="F320" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G320" s="27"/>
+      <c r="G320" s="62"/>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A321" s="27"/>
-      <c r="B321" s="27"/>
+      <c r="A321" s="62"/>
+      <c r="B321" s="62"/>
       <c r="C321" s="16" t="s">
         <v>43</v>
       </c>
@@ -6905,11 +6905,11 @@
       <c r="F321" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G321" s="27"/>
+      <c r="G321" s="62"/>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A322" s="27"/>
-      <c r="B322" s="27"/>
+      <c r="A322" s="62"/>
+      <c r="B322" s="62"/>
       <c r="C322" s="16" t="s">
         <v>13</v>
       </c>
@@ -6922,11 +6922,11 @@
       <c r="F322" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G322" s="27"/>
+      <c r="G322" s="62"/>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A323" s="27"/>
-      <c r="B323" s="27"/>
+      <c r="A323" s="62"/>
+      <c r="B323" s="62"/>
       <c r="C323" s="16" t="s">
         <v>34</v>
       </c>
@@ -6939,11 +6939,11 @@
       <c r="F323" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G323" s="27"/>
+      <c r="G323" s="62"/>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A324" s="27"/>
-      <c r="B324" s="27"/>
+      <c r="A324" s="62"/>
+      <c r="B324" s="62"/>
       <c r="C324" s="16" t="s">
         <v>78</v>
       </c>
@@ -6956,11 +6956,11 @@
       <c r="F324" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G324" s="27"/>
+      <c r="G324" s="62"/>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A325" s="27"/>
-      <c r="B325" s="27"/>
+      <c r="A325" s="62"/>
+      <c r="B325" s="62"/>
       <c r="C325" s="16" t="s">
         <v>79</v>
       </c>
@@ -6973,7 +6973,7 @@
       <c r="F325" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G325" s="27"/>
+      <c r="G325" s="62"/>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" s="15"/>
@@ -6990,13 +6990,13 @@
       <c r="F326" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G326" s="29"/>
+      <c r="G326" s="59"/>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A327" s="41">
+      <c r="A327" s="73">
         <v>21</v>
       </c>
-      <c r="B327" s="42" t="s">
+      <c r="B327" s="74" t="s">
         <v>81</v>
       </c>
       <c r="C327" s="18" t="s">
@@ -7011,13 +7011,13 @@
       <c r="F327" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G327" s="41" t="s">
+      <c r="G327" s="73" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A328" s="41"/>
-      <c r="B328" s="41"/>
+      <c r="A328" s="73"/>
+      <c r="B328" s="73"/>
       <c r="C328" s="18" t="s">
         <v>17</v>
       </c>
@@ -7030,11 +7030,11 @@
       <c r="F328" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G328" s="41"/>
+      <c r="G328" s="73"/>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A329" s="41"/>
-      <c r="B329" s="41"/>
+      <c r="A329" s="73"/>
+      <c r="B329" s="73"/>
       <c r="C329" s="18" t="s">
         <v>84</v>
       </c>
@@ -7047,13 +7047,13 @@
       <c r="F329" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G329" s="41"/>
+      <c r="G329" s="73"/>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A330" s="38">
+      <c r="A330" s="70">
         <v>22</v>
       </c>
-      <c r="B330" s="40" t="s">
+      <c r="B330" s="72" t="s">
         <v>85</v>
       </c>
       <c r="C330" s="20" t="s">
@@ -7068,13 +7068,13 @@
       <c r="F330" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G330" s="38" t="s">
+      <c r="G330" s="70" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A331" s="39"/>
-      <c r="B331" s="39"/>
+      <c r="A331" s="71"/>
+      <c r="B331" s="71"/>
       <c r="C331" s="20" t="s">
         <v>88</v>
       </c>
@@ -7087,11 +7087,11 @@
       <c r="F331" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G331" s="39"/>
+      <c r="G331" s="71"/>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A332" s="39"/>
-      <c r="B332" s="39"/>
+      <c r="A332" s="71"/>
+      <c r="B332" s="71"/>
       <c r="C332" s="20" t="s">
         <v>89</v>
       </c>
@@ -7104,11 +7104,11 @@
       <c r="F332" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G332" s="39"/>
+      <c r="G332" s="71"/>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A333" s="39"/>
-      <c r="B333" s="39"/>
+      <c r="A333" s="71"/>
+      <c r="B333" s="71"/>
       <c r="C333" s="20" t="s">
         <v>90</v>
       </c>
@@ -7121,11 +7121,11 @@
       <c r="F333" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G333" s="39"/>
+      <c r="G333" s="71"/>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A334" s="39"/>
-      <c r="B334" s="39"/>
+      <c r="A334" s="71"/>
+      <c r="B334" s="71"/>
       <c r="C334" s="20" t="s">
         <v>91</v>
       </c>
@@ -7138,11 +7138,11 @@
       <c r="F334" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G334" s="39"/>
+      <c r="G334" s="71"/>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A335" s="39"/>
-      <c r="B335" s="39"/>
+      <c r="A335" s="71"/>
+      <c r="B335" s="71"/>
       <c r="C335" s="20" t="s">
         <v>92</v>
       </c>
@@ -7155,11 +7155,11 @@
       <c r="F335" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G335" s="39"/>
+      <c r="G335" s="71"/>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A336" s="39"/>
-      <c r="B336" s="39"/>
+      <c r="A336" s="71"/>
+      <c r="B336" s="71"/>
       <c r="C336" s="20" t="s">
         <v>93</v>
       </c>
@@ -7172,11 +7172,11 @@
       <c r="F336" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G336" s="39"/>
+      <c r="G336" s="71"/>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A337" s="39"/>
-      <c r="B337" s="39"/>
+      <c r="A337" s="71"/>
+      <c r="B337" s="71"/>
       <c r="C337" s="20" t="s">
         <v>94</v>
       </c>
@@ -7189,11 +7189,11 @@
       <c r="F337" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G337" s="39"/>
+      <c r="G337" s="71"/>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A338" s="39"/>
-      <c r="B338" s="39"/>
+      <c r="A338" s="71"/>
+      <c r="B338" s="71"/>
       <c r="C338" s="20" t="s">
         <v>17</v>
       </c>
@@ -7206,26 +7206,28 @@
       <c r="F338" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G338" s="39"/>
+      <c r="G338" s="71"/>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A339" s="39"/>
-      <c r="B339" s="39"/>
+      <c r="A339" s="71"/>
+      <c r="B339" s="71"/>
       <c r="C339" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="D339" s="21"/>
+      <c r="D339" s="21">
+        <v>0</v>
+      </c>
       <c r="E339" s="21" t="s">
         <v>6</v>
       </c>
       <c r="F339" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G339" s="39"/>
+      <c r="G339" s="71"/>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A340" s="39"/>
-      <c r="B340" s="39"/>
+      <c r="A340" s="71"/>
+      <c r="B340" s="71"/>
       <c r="C340" s="20" t="s">
         <v>32</v>
       </c>
@@ -7238,11 +7240,11 @@
       <c r="F340" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G340" s="39"/>
+      <c r="G340" s="71"/>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A341" s="39"/>
-      <c r="B341" s="39"/>
+      <c r="A341" s="71"/>
+      <c r="B341" s="71"/>
       <c r="C341" s="20" t="s">
         <v>76</v>
       </c>
@@ -7255,13 +7257,13 @@
       <c r="F341" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G341" s="39"/>
+      <c r="G341" s="71"/>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A342" s="38">
+      <c r="A342" s="70">
         <v>23</v>
       </c>
-      <c r="B342" s="40" t="s">
+      <c r="B342" s="72" t="s">
         <v>96</v>
       </c>
       <c r="C342" s="20" t="s">
@@ -7276,13 +7278,13 @@
       <c r="F342" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G342" s="38" t="s">
+      <c r="G342" s="70" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A343" s="39"/>
-      <c r="B343" s="39"/>
+      <c r="A343" s="71"/>
+      <c r="B343" s="71"/>
       <c r="C343" s="20" t="s">
         <v>88</v>
       </c>
@@ -7295,11 +7297,11 @@
       <c r="F343" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G343" s="39"/>
+      <c r="G343" s="71"/>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A344" s="39"/>
-      <c r="B344" s="39"/>
+      <c r="A344" s="71"/>
+      <c r="B344" s="71"/>
       <c r="C344" s="20" t="s">
         <v>89</v>
       </c>
@@ -7312,11 +7314,11 @@
       <c r="F344" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G344" s="39"/>
+      <c r="G344" s="71"/>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A345" s="39"/>
-      <c r="B345" s="39"/>
+      <c r="A345" s="71"/>
+      <c r="B345" s="71"/>
       <c r="C345" s="20" t="s">
         <v>90</v>
       </c>
@@ -7329,11 +7331,11 @@
       <c r="F345" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G345" s="39"/>
+      <c r="G345" s="71"/>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A346" s="39"/>
-      <c r="B346" s="39"/>
+      <c r="A346" s="71"/>
+      <c r="B346" s="71"/>
       <c r="C346" s="20" t="s">
         <v>91</v>
       </c>
@@ -7346,11 +7348,11 @@
       <c r="F346" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G346" s="39"/>
+      <c r="G346" s="71"/>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A347" s="39"/>
-      <c r="B347" s="39"/>
+      <c r="A347" s="71"/>
+      <c r="B347" s="71"/>
       <c r="C347" s="20" t="s">
         <v>92</v>
       </c>
@@ -7363,11 +7365,11 @@
       <c r="F347" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G347" s="39"/>
+      <c r="G347" s="71"/>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A348" s="39"/>
-      <c r="B348" s="39"/>
+      <c r="A348" s="71"/>
+      <c r="B348" s="71"/>
       <c r="C348" s="20" t="s">
         <v>93</v>
       </c>
@@ -7380,11 +7382,11 @@
       <c r="F348" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G348" s="39"/>
+      <c r="G348" s="71"/>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A349" s="39"/>
-      <c r="B349" s="39"/>
+      <c r="A349" s="71"/>
+      <c r="B349" s="71"/>
       <c r="C349" s="20" t="s">
         <v>82</v>
       </c>
@@ -7397,11 +7399,11 @@
       <c r="F349" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G349" s="39"/>
+      <c r="G349" s="71"/>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A350" s="39"/>
-      <c r="B350" s="39"/>
+      <c r="A350" s="71"/>
+      <c r="B350" s="71"/>
       <c r="C350" s="20" t="s">
         <v>17</v>
       </c>
@@ -7414,26 +7416,28 @@
       <c r="F350" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G350" s="39"/>
+      <c r="G350" s="71"/>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A351" s="39"/>
-      <c r="B351" s="39"/>
+      <c r="A351" s="71"/>
+      <c r="B351" s="71"/>
       <c r="C351" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="D351" s="21"/>
+      <c r="D351" s="21">
+        <v>0</v>
+      </c>
       <c r="E351" s="21" t="s">
         <v>6</v>
       </c>
       <c r="F351" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G351" s="39"/>
+      <c r="G351" s="71"/>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A352" s="39"/>
-      <c r="B352" s="39"/>
+      <c r="A352" s="71"/>
+      <c r="B352" s="71"/>
       <c r="C352" s="20" t="s">
         <v>32</v>
       </c>
@@ -7446,11 +7450,11 @@
       <c r="F352" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G352" s="39"/>
+      <c r="G352" s="71"/>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A353" s="39"/>
-      <c r="B353" s="39"/>
+      <c r="A353" s="71"/>
+      <c r="B353" s="71"/>
       <c r="C353" s="20" t="s">
         <v>76</v>
       </c>
@@ -7463,13 +7467,13 @@
       <c r="F353" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G353" s="39"/>
+      <c r="G353" s="71"/>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A354" s="38">
+      <c r="A354" s="70">
         <v>24</v>
       </c>
-      <c r="B354" s="40" t="s">
+      <c r="B354" s="72" t="s">
         <v>97</v>
       </c>
       <c r="C354" s="20" t="s">
@@ -7484,13 +7488,13 @@
       <c r="F354" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G354" s="38" t="s">
+      <c r="G354" s="70" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A355" s="39"/>
-      <c r="B355" s="39"/>
+      <c r="A355" s="71"/>
+      <c r="B355" s="71"/>
       <c r="C355" s="20" t="s">
         <v>88</v>
       </c>
@@ -7503,11 +7507,11 @@
       <c r="F355" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G355" s="39"/>
+      <c r="G355" s="71"/>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A356" s="39"/>
-      <c r="B356" s="39"/>
+      <c r="A356" s="71"/>
+      <c r="B356" s="71"/>
       <c r="C356" s="20" t="s">
         <v>89</v>
       </c>
@@ -7520,11 +7524,11 @@
       <c r="F356" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G356" s="39"/>
+      <c r="G356" s="71"/>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A357" s="39"/>
-      <c r="B357" s="39"/>
+      <c r="A357" s="71"/>
+      <c r="B357" s="71"/>
       <c r="C357" s="20" t="s">
         <v>90</v>
       </c>
@@ -7537,11 +7541,11 @@
       <c r="F357" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G357" s="39"/>
+      <c r="G357" s="71"/>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A358" s="39"/>
-      <c r="B358" s="39"/>
+      <c r="A358" s="71"/>
+      <c r="B358" s="71"/>
       <c r="C358" s="20" t="s">
         <v>91</v>
       </c>
@@ -7554,11 +7558,11 @@
       <c r="F358" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G358" s="39"/>
+      <c r="G358" s="71"/>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A359" s="39"/>
-      <c r="B359" s="39"/>
+      <c r="A359" s="71"/>
+      <c r="B359" s="71"/>
       <c r="C359" s="20" t="s">
         <v>92</v>
       </c>
@@ -7571,11 +7575,11 @@
       <c r="F359" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G359" s="39"/>
+      <c r="G359" s="71"/>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A360" s="39"/>
-      <c r="B360" s="39"/>
+      <c r="A360" s="71"/>
+      <c r="B360" s="71"/>
       <c r="C360" s="20" t="s">
         <v>93</v>
       </c>
@@ -7588,11 +7592,11 @@
       <c r="F360" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G360" s="39"/>
+      <c r="G360" s="71"/>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A361" s="39"/>
-      <c r="B361" s="39"/>
+      <c r="A361" s="71"/>
+      <c r="B361" s="71"/>
       <c r="C361" s="20" t="s">
         <v>98</v>
       </c>
@@ -7605,11 +7609,11 @@
       <c r="F361" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G361" s="39"/>
+      <c r="G361" s="71"/>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A362" s="39"/>
-      <c r="B362" s="39"/>
+      <c r="A362" s="71"/>
+      <c r="B362" s="71"/>
       <c r="C362" s="20" t="s">
         <v>17</v>
       </c>
@@ -7622,26 +7626,28 @@
       <c r="F362" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G362" s="39"/>
+      <c r="G362" s="71"/>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A363" s="39"/>
-      <c r="B363" s="39"/>
+      <c r="A363" s="71"/>
+      <c r="B363" s="71"/>
       <c r="C363" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="D363" s="21"/>
+      <c r="D363" s="21">
+        <v>0</v>
+      </c>
       <c r="E363" s="21" t="s">
         <v>6</v>
       </c>
       <c r="F363" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G363" s="39"/>
+      <c r="G363" s="71"/>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A364" s="39"/>
-      <c r="B364" s="39"/>
+      <c r="A364" s="71"/>
+      <c r="B364" s="71"/>
       <c r="C364" s="20" t="s">
         <v>61</v>
       </c>
@@ -7654,11 +7660,11 @@
       <c r="F364" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G364" s="39"/>
+      <c r="G364" s="71"/>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A365" s="39"/>
-      <c r="B365" s="39"/>
+      <c r="A365" s="71"/>
+      <c r="B365" s="71"/>
       <c r="C365" s="20" t="s">
         <v>99</v>
       </c>
@@ -7671,13 +7677,13 @@
       <c r="F365" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G365" s="39"/>
+      <c r="G365" s="71"/>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A366" s="30">
+      <c r="A366" s="75">
         <v>25</v>
       </c>
-      <c r="B366" s="33" t="s">
+      <c r="B366" s="78" t="s">
         <v>100</v>
       </c>
       <c r="C366" s="22" t="s">
@@ -7692,13 +7698,13 @@
       <c r="F366" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G366" s="30" t="s">
+      <c r="G366" s="75" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A367" s="31"/>
-      <c r="B367" s="31"/>
+      <c r="A367" s="76"/>
+      <c r="B367" s="76"/>
       <c r="C367" s="22" t="s">
         <v>103</v>
       </c>
@@ -7711,11 +7717,11 @@
       <c r="F367" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G367" s="31"/>
+      <c r="G367" s="76"/>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A368" s="31"/>
-      <c r="B368" s="31"/>
+      <c r="A368" s="76"/>
+      <c r="B368" s="76"/>
       <c r="C368" s="22" t="s">
         <v>104</v>
       </c>
@@ -7728,11 +7734,11 @@
       <c r="F368" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G368" s="31"/>
+      <c r="G368" s="76"/>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A369" s="31"/>
-      <c r="B369" s="31"/>
+      <c r="A369" s="76"/>
+      <c r="B369" s="76"/>
       <c r="C369" s="22" t="s">
         <v>105</v>
       </c>
@@ -7745,11 +7751,11 @@
       <c r="F369" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G369" s="31"/>
+      <c r="G369" s="76"/>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A370" s="32"/>
-      <c r="B370" s="32"/>
+      <c r="A370" s="77"/>
+      <c r="B370" s="77"/>
       <c r="C370" s="22" t="s">
         <v>106</v>
       </c>
@@ -7762,13 +7768,13 @@
       <c r="F370" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G370" s="32"/>
+      <c r="G370" s="77"/>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A371" s="30">
+      <c r="A371" s="75">
         <v>26</v>
       </c>
-      <c r="B371" s="33" t="s">
+      <c r="B371" s="78" t="s">
         <v>107</v>
       </c>
       <c r="C371" s="22" t="s">
@@ -7783,13 +7789,13 @@
       <c r="F371" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G371" s="30" t="s">
+      <c r="G371" s="75" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A372" s="31"/>
-      <c r="B372" s="31"/>
+      <c r="A372" s="76"/>
+      <c r="B372" s="76"/>
       <c r="C372" s="22" t="s">
         <v>103</v>
       </c>
@@ -7802,11 +7808,11 @@
       <c r="F372" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G372" s="31"/>
+      <c r="G372" s="76"/>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A373" s="31"/>
-      <c r="B373" s="31"/>
+      <c r="A373" s="76"/>
+      <c r="B373" s="76"/>
       <c r="C373" s="22" t="s">
         <v>104</v>
       </c>
@@ -7819,11 +7825,11 @@
       <c r="F373" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G373" s="31"/>
+      <c r="G373" s="76"/>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A374" s="31"/>
-      <c r="B374" s="31"/>
+      <c r="A374" s="76"/>
+      <c r="B374" s="76"/>
       <c r="C374" s="22" t="s">
         <v>105</v>
       </c>
@@ -7836,11 +7842,11 @@
       <c r="F374" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G374" s="31"/>
+      <c r="G374" s="76"/>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A375" s="32"/>
-      <c r="B375" s="32"/>
+      <c r="A375" s="77"/>
+      <c r="B375" s="77"/>
       <c r="C375" s="22" t="s">
         <v>106</v>
       </c>
@@ -7853,13 +7859,13 @@
       <c r="F375" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G375" s="32"/>
+      <c r="G375" s="77"/>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A376" s="30">
+      <c r="A376" s="75">
         <v>27</v>
       </c>
-      <c r="B376" s="33" t="s">
+      <c r="B376" s="78" t="s">
         <v>108</v>
       </c>
       <c r="C376" s="22" t="s">
@@ -7874,13 +7880,13 @@
       <c r="F376" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G376" s="30" t="s">
+      <c r="G376" s="75" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A377" s="31"/>
-      <c r="B377" s="31"/>
+      <c r="A377" s="76"/>
+      <c r="B377" s="76"/>
       <c r="C377" s="22" t="s">
         <v>103</v>
       </c>
@@ -7893,11 +7899,11 @@
       <c r="F377" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G377" s="31"/>
+      <c r="G377" s="76"/>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A378" s="31"/>
-      <c r="B378" s="31"/>
+      <c r="A378" s="76"/>
+      <c r="B378" s="76"/>
       <c r="C378" s="22" t="s">
         <v>104</v>
       </c>
@@ -7910,11 +7916,11 @@
       <c r="F378" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G378" s="31"/>
+      <c r="G378" s="76"/>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A379" s="31"/>
-      <c r="B379" s="31"/>
+      <c r="A379" s="76"/>
+      <c r="B379" s="76"/>
       <c r="C379" s="22" t="s">
         <v>105</v>
       </c>
@@ -7927,11 +7933,11 @@
       <c r="F379" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G379" s="31"/>
+      <c r="G379" s="76"/>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A380" s="32"/>
-      <c r="B380" s="32"/>
+      <c r="A380" s="77"/>
+      <c r="B380" s="77"/>
       <c r="C380" s="22" t="s">
         <v>106</v>
       </c>
@@ -7944,13 +7950,13 @@
       <c r="F380" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G380" s="32"/>
+      <c r="G380" s="77"/>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A381" s="34">
+      <c r="A381" s="79">
         <v>28</v>
       </c>
-      <c r="B381" s="37" t="s">
+      <c r="B381" s="82" t="s">
         <v>109</v>
       </c>
       <c r="C381" s="24" t="s">
@@ -7965,13 +7971,13 @@
       <c r="F381" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G381" s="34" t="s">
+      <c r="G381" s="79" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A382" s="35"/>
-      <c r="B382" s="35"/>
+      <c r="A382" s="80"/>
+      <c r="B382" s="80"/>
       <c r="C382" s="24" t="s">
         <v>76</v>
       </c>
@@ -7984,11 +7990,11 @@
       <c r="F382" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="G382" s="35"/>
+      <c r="G382" s="80"/>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A383" s="36"/>
-      <c r="B383" s="36"/>
+      <c r="A383" s="81"/>
+      <c r="B383" s="81"/>
       <c r="C383" s="24" t="s">
         <v>112</v>
       </c>
@@ -8001,13 +8007,13 @@
       <c r="F383" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="G383" s="36"/>
+      <c r="G383" s="81"/>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A384" s="26">
+      <c r="A384" s="65">
         <v>29</v>
       </c>
-      <c r="B384" s="28" t="s">
+      <c r="B384" s="66" t="s">
         <v>113</v>
       </c>
       <c r="C384" s="16" t="s">
@@ -8022,13 +8028,13 @@
       <c r="F384" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G384" s="26" t="s">
+      <c r="G384" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A385" s="27"/>
-      <c r="B385" s="27"/>
+      <c r="A385" s="62"/>
+      <c r="B385" s="62"/>
       <c r="C385" s="13" t="s">
         <v>88</v>
       </c>
@@ -8041,11 +8047,11 @@
       <c r="F385" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G385" s="27"/>
+      <c r="G385" s="62"/>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A386" s="27"/>
-      <c r="B386" s="27"/>
+      <c r="A386" s="62"/>
+      <c r="B386" s="62"/>
       <c r="C386" s="13" t="s">
         <v>89</v>
       </c>
@@ -8058,11 +8064,11 @@
       <c r="F386" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G386" s="27"/>
+      <c r="G386" s="62"/>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A387" s="27"/>
-      <c r="B387" s="27"/>
+      <c r="A387" s="62"/>
+      <c r="B387" s="62"/>
       <c r="C387" s="13" t="s">
         <v>90</v>
       </c>
@@ -8075,11 +8081,11 @@
       <c r="F387" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G387" s="27"/>
+      <c r="G387" s="62"/>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A388" s="27"/>
-      <c r="B388" s="27"/>
+      <c r="A388" s="62"/>
+      <c r="B388" s="62"/>
       <c r="C388" s="13" t="s">
         <v>91</v>
       </c>
@@ -8092,11 +8098,11 @@
       <c r="F388" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G388" s="27"/>
+      <c r="G388" s="62"/>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A389" s="27"/>
-      <c r="B389" s="27"/>
+      <c r="A389" s="62"/>
+      <c r="B389" s="62"/>
       <c r="C389" s="13" t="s">
         <v>92</v>
       </c>
@@ -8109,11 +8115,11 @@
       <c r="F389" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G389" s="27"/>
+      <c r="G389" s="62"/>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A390" s="27"/>
-      <c r="B390" s="27"/>
+      <c r="A390" s="62"/>
+      <c r="B390" s="62"/>
       <c r="C390" s="13" t="s">
         <v>93</v>
       </c>
@@ -8126,11 +8132,11 @@
       <c r="F390" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G390" s="27"/>
+      <c r="G390" s="62"/>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A391" s="27"/>
-      <c r="B391" s="27"/>
+      <c r="A391" s="62"/>
+      <c r="B391" s="62"/>
       <c r="C391" s="13" t="s">
         <v>82</v>
       </c>
@@ -8143,11 +8149,11 @@
       <c r="F391" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G391" s="27"/>
+      <c r="G391" s="62"/>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A392" s="27"/>
-      <c r="B392" s="27"/>
+      <c r="A392" s="62"/>
+      <c r="B392" s="62"/>
       <c r="C392" s="13" t="s">
         <v>17</v>
       </c>
@@ -8160,26 +8166,28 @@
       <c r="F392" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G392" s="27"/>
+      <c r="G392" s="62"/>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A393" s="27"/>
-      <c r="B393" s="27"/>
+      <c r="A393" s="62"/>
+      <c r="B393" s="62"/>
       <c r="C393" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D393" s="14"/>
+      <c r="D393" s="14">
+        <v>0</v>
+      </c>
       <c r="E393" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F393" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G393" s="27"/>
+      <c r="G393" s="62"/>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A394" s="27"/>
-      <c r="B394" s="27"/>
+      <c r="A394" s="62"/>
+      <c r="B394" s="62"/>
       <c r="C394" s="16" t="s">
         <v>32</v>
       </c>
@@ -8192,11 +8200,11 @@
       <c r="F394" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G394" s="27"/>
+      <c r="G394" s="62"/>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A395" s="27"/>
-      <c r="B395" s="27"/>
+      <c r="A395" s="62"/>
+      <c r="B395" s="62"/>
       <c r="C395" s="16" t="s">
         <v>76</v>
       </c>
@@ -8209,11 +8217,11 @@
       <c r="F395" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G395" s="27"/>
+      <c r="G395" s="62"/>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A396" s="27"/>
-      <c r="B396" s="27"/>
+      <c r="A396" s="62"/>
+      <c r="B396" s="62"/>
       <c r="C396" s="16" t="s">
         <v>110</v>
       </c>
@@ -8226,11 +8234,11 @@
       <c r="F396" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G396" s="27"/>
+      <c r="G396" s="62"/>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A397" s="29"/>
-      <c r="B397" s="29"/>
+      <c r="A397" s="59"/>
+      <c r="B397" s="59"/>
       <c r="C397" s="16" t="s">
         <v>115</v>
       </c>
@@ -8243,13 +8251,13 @@
       <c r="F397" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G397" s="29"/>
+      <c r="G397" s="59"/>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A398" s="26">
+      <c r="A398" s="65">
         <v>30</v>
       </c>
-      <c r="B398" s="28" t="s">
+      <c r="B398" s="66" t="s">
         <v>116</v>
       </c>
       <c r="C398" s="16" t="s">
@@ -8264,13 +8272,13 @@
       <c r="F398" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G398" s="26" t="s">
+      <c r="G398" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A399" s="27"/>
-      <c r="B399" s="27"/>
+      <c r="A399" s="62"/>
+      <c r="B399" s="62"/>
       <c r="C399" s="16" t="s">
         <v>88</v>
       </c>
@@ -8283,11 +8291,11 @@
       <c r="F399" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G399" s="27"/>
+      <c r="G399" s="62"/>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A400" s="27"/>
-      <c r="B400" s="27"/>
+      <c r="A400" s="62"/>
+      <c r="B400" s="62"/>
       <c r="C400" s="16" t="s">
         <v>89</v>
       </c>
@@ -8300,11 +8308,11 @@
       <c r="F400" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G400" s="27"/>
+      <c r="G400" s="62"/>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A401" s="27"/>
-      <c r="B401" s="27"/>
+      <c r="A401" s="62"/>
+      <c r="B401" s="62"/>
       <c r="C401" s="16" t="s">
         <v>90</v>
       </c>
@@ -8317,11 +8325,11 @@
       <c r="F401" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G401" s="27"/>
+      <c r="G401" s="62"/>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A402" s="27"/>
-      <c r="B402" s="27"/>
+      <c r="A402" s="62"/>
+      <c r="B402" s="62"/>
       <c r="C402" s="13" t="s">
         <v>91</v>
       </c>
@@ -8334,11 +8342,11 @@
       <c r="F402" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G402" s="27"/>
+      <c r="G402" s="62"/>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A403" s="27"/>
-      <c r="B403" s="27"/>
+      <c r="A403" s="62"/>
+      <c r="B403" s="62"/>
       <c r="C403" s="13" t="s">
         <v>92</v>
       </c>
@@ -8351,11 +8359,11 @@
       <c r="F403" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G403" s="27"/>
+      <c r="G403" s="62"/>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A404" s="27"/>
-      <c r="B404" s="27"/>
+      <c r="A404" s="62"/>
+      <c r="B404" s="62"/>
       <c r="C404" s="13" t="s">
         <v>93</v>
       </c>
@@ -8368,11 +8376,11 @@
       <c r="F404" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G404" s="27"/>
+      <c r="G404" s="62"/>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A405" s="27"/>
-      <c r="B405" s="27"/>
+      <c r="A405" s="62"/>
+      <c r="B405" s="62"/>
       <c r="C405" s="13" t="s">
         <v>117</v>
       </c>
@@ -8385,11 +8393,11 @@
       <c r="F405" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G405" s="27"/>
+      <c r="G405" s="62"/>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A406" s="27"/>
-      <c r="B406" s="27"/>
+      <c r="A406" s="62"/>
+      <c r="B406" s="62"/>
       <c r="C406" s="13" t="s">
         <v>17</v>
       </c>
@@ -8402,26 +8410,28 @@
       <c r="F406" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G406" s="27"/>
+      <c r="G406" s="62"/>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A407" s="27"/>
-      <c r="B407" s="27"/>
+      <c r="A407" s="62"/>
+      <c r="B407" s="62"/>
       <c r="C407" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D407" s="14"/>
+      <c r="D407" s="14">
+        <v>0</v>
+      </c>
       <c r="E407" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F407" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G407" s="27"/>
+      <c r="G407" s="62"/>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A408" s="27"/>
-      <c r="B408" s="27"/>
+      <c r="A408" s="62"/>
+      <c r="B408" s="62"/>
       <c r="C408" s="13" t="s">
         <v>32</v>
       </c>
@@ -8434,11 +8444,11 @@
       <c r="F408" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G408" s="27"/>
+      <c r="G408" s="62"/>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A409" s="27"/>
-      <c r="B409" s="27"/>
+      <c r="A409" s="62"/>
+      <c r="B409" s="62"/>
       <c r="C409" s="13" t="s">
         <v>76</v>
       </c>
@@ -8451,11 +8461,11 @@
       <c r="F409" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G409" s="27"/>
+      <c r="G409" s="62"/>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A410" s="27"/>
-      <c r="B410" s="27"/>
+      <c r="A410" s="62"/>
+      <c r="B410" s="62"/>
       <c r="C410" s="13" t="s">
         <v>110</v>
       </c>
@@ -8468,13 +8478,13 @@
       <c r="F410" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G410" s="27"/>
+      <c r="G410" s="62"/>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A411" s="26">
+      <c r="A411" s="65">
         <v>31</v>
       </c>
-      <c r="B411" s="28" t="s">
+      <c r="B411" s="66" t="s">
         <v>118</v>
       </c>
       <c r="C411" s="13" t="s">
@@ -8489,13 +8499,13 @@
       <c r="F411" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G411" s="26" t="s">
+      <c r="G411" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A412" s="27"/>
-      <c r="B412" s="27"/>
+      <c r="A412" s="62"/>
+      <c r="B412" s="62"/>
       <c r="C412" s="13" t="s">
         <v>88</v>
       </c>
@@ -8508,11 +8518,11 @@
       <c r="F412" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G412" s="27"/>
+      <c r="G412" s="62"/>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A413" s="27"/>
-      <c r="B413" s="27"/>
+      <c r="A413" s="62"/>
+      <c r="B413" s="62"/>
       <c r="C413" s="13" t="s">
         <v>89</v>
       </c>
@@ -8525,11 +8535,11 @@
       <c r="F413" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G413" s="27"/>
+      <c r="G413" s="62"/>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A414" s="27"/>
-      <c r="B414" s="27"/>
+      <c r="A414" s="62"/>
+      <c r="B414" s="62"/>
       <c r="C414" s="13" t="s">
         <v>90</v>
       </c>
@@ -8542,11 +8552,11 @@
       <c r="F414" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G414" s="27"/>
+      <c r="G414" s="62"/>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A415" s="27"/>
-      <c r="B415" s="27"/>
+      <c r="A415" s="62"/>
+      <c r="B415" s="62"/>
       <c r="C415" s="13" t="s">
         <v>91</v>
       </c>
@@ -8559,11 +8569,11 @@
       <c r="F415" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G415" s="27"/>
+      <c r="G415" s="62"/>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A416" s="27"/>
-      <c r="B416" s="27"/>
+      <c r="A416" s="62"/>
+      <c r="B416" s="62"/>
       <c r="C416" s="13" t="s">
         <v>92</v>
       </c>
@@ -8576,11 +8586,11 @@
       <c r="F416" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G416" s="27"/>
+      <c r="G416" s="62"/>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A417" s="27"/>
-      <c r="B417" s="27"/>
+      <c r="A417" s="62"/>
+      <c r="B417" s="62"/>
       <c r="C417" s="13" t="s">
         <v>93</v>
       </c>
@@ -8593,11 +8603,11 @@
       <c r="F417" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G417" s="27"/>
+      <c r="G417" s="62"/>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A418" s="27"/>
-      <c r="B418" s="27"/>
+      <c r="A418" s="62"/>
+      <c r="B418" s="62"/>
       <c r="C418" s="13" t="s">
         <v>98</v>
       </c>
@@ -8610,11 +8620,11 @@
       <c r="F418" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G418" s="27"/>
+      <c r="G418" s="62"/>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A419" s="27"/>
-      <c r="B419" s="27"/>
+      <c r="A419" s="62"/>
+      <c r="B419" s="62"/>
       <c r="C419" s="13" t="s">
         <v>17</v>
       </c>
@@ -8627,26 +8637,28 @@
       <c r="F419" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G419" s="27"/>
+      <c r="G419" s="62"/>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A420" s="27"/>
-      <c r="B420" s="27"/>
+      <c r="A420" s="62"/>
+      <c r="B420" s="62"/>
       <c r="C420" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D420" s="14"/>
+      <c r="D420" s="14">
+        <v>0</v>
+      </c>
       <c r="E420" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F420" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G420" s="27"/>
+      <c r="G420" s="62"/>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A421" s="27"/>
-      <c r="B421" s="27"/>
+      <c r="A421" s="62"/>
+      <c r="B421" s="62"/>
       <c r="C421" s="13" t="s">
         <v>61</v>
       </c>
@@ -8659,11 +8671,11 @@
       <c r="F421" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G421" s="27"/>
+      <c r="G421" s="62"/>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A422" s="27"/>
-      <c r="B422" s="27"/>
+      <c r="A422" s="62"/>
+      <c r="B422" s="62"/>
       <c r="C422" s="13" t="s">
         <v>99</v>
       </c>
@@ -8676,11 +8688,11 @@
       <c r="F422" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G422" s="27"/>
+      <c r="G422" s="62"/>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A423" s="27"/>
-      <c r="B423" s="27"/>
+      <c r="A423" s="62"/>
+      <c r="B423" s="62"/>
       <c r="C423" s="13" t="s">
         <v>110</v>
       </c>
@@ -8693,13 +8705,13 @@
       <c r="F423" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G423" s="27"/>
+      <c r="G423" s="62"/>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A424" s="26">
+      <c r="A424" s="65">
         <v>32</v>
       </c>
-      <c r="B424" s="28" t="s">
+      <c r="B424" s="66" t="s">
         <v>119</v>
       </c>
       <c r="C424" s="13" t="s">
@@ -8714,13 +8726,13 @@
       <c r="F424" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G424" s="26" t="s">
+      <c r="G424" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A425" s="27"/>
-      <c r="B425" s="27"/>
+      <c r="A425" s="62"/>
+      <c r="B425" s="62"/>
       <c r="C425" s="13" t="s">
         <v>88</v>
       </c>
@@ -8733,11 +8745,11 @@
       <c r="F425" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G425" s="27"/>
+      <c r="G425" s="62"/>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A426" s="27"/>
-      <c r="B426" s="27"/>
+      <c r="A426" s="62"/>
+      <c r="B426" s="62"/>
       <c r="C426" s="13" t="s">
         <v>89</v>
       </c>
@@ -8750,11 +8762,11 @@
       <c r="F426" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G426" s="27"/>
+      <c r="G426" s="62"/>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A427" s="27"/>
-      <c r="B427" s="27"/>
+      <c r="A427" s="62"/>
+      <c r="B427" s="62"/>
       <c r="C427" s="13" t="s">
         <v>90</v>
       </c>
@@ -8767,11 +8779,11 @@
       <c r="F427" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G427" s="27"/>
+      <c r="G427" s="62"/>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A428" s="27"/>
-      <c r="B428" s="27"/>
+      <c r="A428" s="62"/>
+      <c r="B428" s="62"/>
       <c r="C428" s="13" t="s">
         <v>91</v>
       </c>
@@ -8784,11 +8796,11 @@
       <c r="F428" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G428" s="27"/>
+      <c r="G428" s="62"/>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A429" s="27"/>
-      <c r="B429" s="27"/>
+      <c r="A429" s="62"/>
+      <c r="B429" s="62"/>
       <c r="C429" s="13" t="s">
         <v>92</v>
       </c>
@@ -8801,11 +8813,11 @@
       <c r="F429" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G429" s="27"/>
+      <c r="G429" s="62"/>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A430" s="27"/>
-      <c r="B430" s="27"/>
+      <c r="A430" s="62"/>
+      <c r="B430" s="62"/>
       <c r="C430" s="13" t="s">
         <v>93</v>
       </c>
@@ -8818,11 +8830,11 @@
       <c r="F430" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G430" s="27"/>
+      <c r="G430" s="62"/>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A431" s="27"/>
-      <c r="B431" s="27"/>
+      <c r="A431" s="62"/>
+      <c r="B431" s="62"/>
       <c r="C431" s="13" t="s">
         <v>82</v>
       </c>
@@ -8835,11 +8847,11 @@
       <c r="F431" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G431" s="27"/>
+      <c r="G431" s="62"/>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A432" s="27"/>
-      <c r="B432" s="27"/>
+      <c r="A432" s="62"/>
+      <c r="B432" s="62"/>
       <c r="C432" s="13" t="s">
         <v>17</v>
       </c>
@@ -8852,26 +8864,28 @@
       <c r="F432" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G432" s="27"/>
+      <c r="G432" s="62"/>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A433" s="27"/>
-      <c r="B433" s="27"/>
+      <c r="A433" s="62"/>
+      <c r="B433" s="62"/>
       <c r="C433" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D433" s="14"/>
+      <c r="D433" s="14">
+        <v>0</v>
+      </c>
       <c r="E433" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F433" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G433" s="27"/>
+      <c r="G433" s="62"/>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A434" s="27"/>
-      <c r="B434" s="27"/>
+      <c r="A434" s="62"/>
+      <c r="B434" s="62"/>
       <c r="C434" s="13" t="s">
         <v>32</v>
       </c>
@@ -8884,11 +8898,11 @@
       <c r="F434" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G434" s="27"/>
+      <c r="G434" s="62"/>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A435" s="27"/>
-      <c r="B435" s="27"/>
+      <c r="A435" s="62"/>
+      <c r="B435" s="62"/>
       <c r="C435" s="13" t="s">
         <v>76</v>
       </c>
@@ -8901,11 +8915,11 @@
       <c r="F435" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G435" s="27"/>
+      <c r="G435" s="62"/>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A436" s="27"/>
-      <c r="B436" s="27"/>
+      <c r="A436" s="62"/>
+      <c r="B436" s="62"/>
       <c r="C436" s="13" t="s">
         <v>110</v>
       </c>
@@ -8918,11 +8932,11 @@
       <c r="F436" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G436" s="27"/>
+      <c r="G436" s="62"/>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A437" s="29"/>
-      <c r="B437" s="29"/>
+      <c r="A437" s="59"/>
+      <c r="B437" s="59"/>
       <c r="C437" s="13" t="s">
         <v>115</v>
       </c>
@@ -8935,13 +8949,13 @@
       <c r="F437" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G437" s="29"/>
+      <c r="G437" s="59"/>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A438" s="26">
+      <c r="A438" s="65">
         <v>33</v>
       </c>
-      <c r="B438" s="28" t="s">
+      <c r="B438" s="66" t="s">
         <v>120</v>
       </c>
       <c r="C438" s="13" t="s">
@@ -8956,13 +8970,13 @@
       <c r="F438" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G438" s="26" t="s">
+      <c r="G438" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A439" s="27"/>
-      <c r="B439" s="27"/>
+      <c r="A439" s="62"/>
+      <c r="B439" s="62"/>
       <c r="C439" s="13" t="s">
         <v>88</v>
       </c>
@@ -8975,11 +8989,11 @@
       <c r="F439" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G439" s="27"/>
+      <c r="G439" s="62"/>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A440" s="27"/>
-      <c r="B440" s="27"/>
+      <c r="A440" s="62"/>
+      <c r="B440" s="62"/>
       <c r="C440" s="13" t="s">
         <v>89</v>
       </c>
@@ -8992,11 +9006,11 @@
       <c r="F440" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G440" s="27"/>
+      <c r="G440" s="62"/>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A441" s="27"/>
-      <c r="B441" s="27"/>
+      <c r="A441" s="62"/>
+      <c r="B441" s="62"/>
       <c r="C441" s="13" t="s">
         <v>90</v>
       </c>
@@ -9009,11 +9023,11 @@
       <c r="F441" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G441" s="27"/>
+      <c r="G441" s="62"/>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A442" s="27"/>
-      <c r="B442" s="27"/>
+      <c r="A442" s="62"/>
+      <c r="B442" s="62"/>
       <c r="C442" s="13" t="s">
         <v>91</v>
       </c>
@@ -9026,11 +9040,11 @@
       <c r="F442" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G442" s="27"/>
+      <c r="G442" s="62"/>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A443" s="27"/>
-      <c r="B443" s="27"/>
+      <c r="A443" s="62"/>
+      <c r="B443" s="62"/>
       <c r="C443" s="13" t="s">
         <v>92</v>
       </c>
@@ -9043,11 +9057,11 @@
       <c r="F443" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G443" s="27"/>
+      <c r="G443" s="62"/>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A444" s="27"/>
-      <c r="B444" s="27"/>
+      <c r="A444" s="62"/>
+      <c r="B444" s="62"/>
       <c r="C444" s="13" t="s">
         <v>93</v>
       </c>
@@ -9060,11 +9074,11 @@
       <c r="F444" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G444" s="27"/>
+      <c r="G444" s="62"/>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A445" s="27"/>
-      <c r="B445" s="27"/>
+      <c r="A445" s="62"/>
+      <c r="B445" s="62"/>
       <c r="C445" s="13" t="s">
         <v>117</v>
       </c>
@@ -9077,11 +9091,11 @@
       <c r="F445" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G445" s="27"/>
+      <c r="G445" s="62"/>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A446" s="27"/>
-      <c r="B446" s="27"/>
+      <c r="A446" s="62"/>
+      <c r="B446" s="62"/>
       <c r="C446" s="13" t="s">
         <v>17</v>
       </c>
@@ -9094,26 +9108,28 @@
       <c r="F446" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G446" s="27"/>
+      <c r="G446" s="62"/>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A447" s="27"/>
-      <c r="B447" s="27"/>
+      <c r="A447" s="62"/>
+      <c r="B447" s="62"/>
       <c r="C447" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D447" s="14"/>
+      <c r="D447" s="14">
+        <v>0</v>
+      </c>
       <c r="E447" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F447" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G447" s="27"/>
+      <c r="G447" s="62"/>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A448" s="27"/>
-      <c r="B448" s="27"/>
+      <c r="A448" s="62"/>
+      <c r="B448" s="62"/>
       <c r="C448" s="13" t="s">
         <v>32</v>
       </c>
@@ -9126,11 +9142,11 @@
       <c r="F448" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G448" s="27"/>
+      <c r="G448" s="62"/>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A449" s="27"/>
-      <c r="B449" s="27"/>
+      <c r="A449" s="62"/>
+      <c r="B449" s="62"/>
       <c r="C449" s="13" t="s">
         <v>76</v>
       </c>
@@ -9143,11 +9159,11 @@
       <c r="F449" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G449" s="27"/>
+      <c r="G449" s="62"/>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A450" s="27"/>
-      <c r="B450" s="27"/>
+      <c r="A450" s="62"/>
+      <c r="B450" s="62"/>
       <c r="C450" s="13" t="s">
         <v>110</v>
       </c>
@@ -9160,13 +9176,13 @@
       <c r="F450" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G450" s="27"/>
+      <c r="G450" s="62"/>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A451" s="26">
+      <c r="A451" s="65">
         <v>34</v>
       </c>
-      <c r="B451" s="28" t="s">
+      <c r="B451" s="66" t="s">
         <v>121</v>
       </c>
       <c r="C451" s="13" t="s">
@@ -9181,13 +9197,13 @@
       <c r="F451" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G451" s="26" t="s">
+      <c r="G451" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A452" s="27"/>
-      <c r="B452" s="27"/>
+      <c r="A452" s="62"/>
+      <c r="B452" s="62"/>
       <c r="C452" s="13" t="s">
         <v>88</v>
       </c>
@@ -9200,11 +9216,11 @@
       <c r="F452" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G452" s="27"/>
+      <c r="G452" s="62"/>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A453" s="27"/>
-      <c r="B453" s="27"/>
+      <c r="A453" s="62"/>
+      <c r="B453" s="62"/>
       <c r="C453" s="13" t="s">
         <v>89</v>
       </c>
@@ -9217,11 +9233,11 @@
       <c r="F453" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G453" s="27"/>
+      <c r="G453" s="62"/>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A454" s="27"/>
-      <c r="B454" s="27"/>
+      <c r="A454" s="62"/>
+      <c r="B454" s="62"/>
       <c r="C454" s="13" t="s">
         <v>90</v>
       </c>
@@ -9234,11 +9250,11 @@
       <c r="F454" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G454" s="27"/>
+      <c r="G454" s="62"/>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A455" s="27"/>
-      <c r="B455" s="27"/>
+      <c r="A455" s="62"/>
+      <c r="B455" s="62"/>
       <c r="C455" s="13" t="s">
         <v>91</v>
       </c>
@@ -9251,11 +9267,11 @@
       <c r="F455" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G455" s="27"/>
+      <c r="G455" s="62"/>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A456" s="27"/>
-      <c r="B456" s="27"/>
+      <c r="A456" s="62"/>
+      <c r="B456" s="62"/>
       <c r="C456" s="13" t="s">
         <v>92</v>
       </c>
@@ -9268,11 +9284,11 @@
       <c r="F456" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G456" s="27"/>
+      <c r="G456" s="62"/>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A457" s="27"/>
-      <c r="B457" s="27"/>
+      <c r="A457" s="62"/>
+      <c r="B457" s="62"/>
       <c r="C457" s="13" t="s">
         <v>93</v>
       </c>
@@ -9285,11 +9301,11 @@
       <c r="F457" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G457" s="27"/>
+      <c r="G457" s="62"/>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A458" s="27"/>
-      <c r="B458" s="27"/>
+      <c r="A458" s="62"/>
+      <c r="B458" s="62"/>
       <c r="C458" s="13" t="s">
         <v>98</v>
       </c>
@@ -9302,11 +9318,11 @@
       <c r="F458" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G458" s="27"/>
+      <c r="G458" s="62"/>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A459" s="27"/>
-      <c r="B459" s="27"/>
+      <c r="A459" s="62"/>
+      <c r="B459" s="62"/>
       <c r="C459" s="13" t="s">
         <v>17</v>
       </c>
@@ -9319,26 +9335,28 @@
       <c r="F459" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G459" s="27"/>
+      <c r="G459" s="62"/>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A460" s="27"/>
-      <c r="B460" s="27"/>
+      <c r="A460" s="62"/>
+      <c r="B460" s="62"/>
       <c r="C460" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D460" s="14"/>
+      <c r="D460" s="14">
+        <v>0</v>
+      </c>
       <c r="E460" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F460" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G460" s="27"/>
+      <c r="G460" s="62"/>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A461" s="27"/>
-      <c r="B461" s="27"/>
+      <c r="A461" s="62"/>
+      <c r="B461" s="62"/>
       <c r="C461" s="13" t="s">
         <v>61</v>
       </c>
@@ -9351,11 +9369,11 @@
       <c r="F461" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G461" s="27"/>
+      <c r="G461" s="62"/>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A462" s="27"/>
-      <c r="B462" s="27"/>
+      <c r="A462" s="62"/>
+      <c r="B462" s="62"/>
       <c r="C462" s="13" t="s">
         <v>99</v>
       </c>
@@ -9368,11 +9386,11 @@
       <c r="F462" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G462" s="27"/>
+      <c r="G462" s="62"/>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A463" s="27"/>
-      <c r="B463" s="27"/>
+      <c r="A463" s="62"/>
+      <c r="B463" s="62"/>
       <c r="C463" s="13" t="s">
         <v>110</v>
       </c>
@@ -9385,13 +9403,13 @@
       <c r="F463" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G463" s="27"/>
+      <c r="G463" s="62"/>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A464" s="26">
+      <c r="A464" s="65">
         <v>35</v>
       </c>
-      <c r="B464" s="28" t="s">
+      <c r="B464" s="66" t="s">
         <v>122</v>
       </c>
       <c r="C464" s="13" t="s">
@@ -9406,13 +9424,13 @@
       <c r="F464" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G464" s="26" t="s">
+      <c r="G464" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A465" s="27"/>
-      <c r="B465" s="27"/>
+      <c r="A465" s="62"/>
+      <c r="B465" s="62"/>
       <c r="C465" s="13" t="s">
         <v>88</v>
       </c>
@@ -9425,11 +9443,11 @@
       <c r="F465" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G465" s="27"/>
+      <c r="G465" s="62"/>
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A466" s="27"/>
-      <c r="B466" s="27"/>
+      <c r="A466" s="62"/>
+      <c r="B466" s="62"/>
       <c r="C466" s="13" t="s">
         <v>89</v>
       </c>
@@ -9442,11 +9460,11 @@
       <c r="F466" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G466" s="27"/>
+      <c r="G466" s="62"/>
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A467" s="27"/>
-      <c r="B467" s="27"/>
+      <c r="A467" s="62"/>
+      <c r="B467" s="62"/>
       <c r="C467" s="13" t="s">
         <v>90</v>
       </c>
@@ -9459,11 +9477,11 @@
       <c r="F467" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G467" s="27"/>
+      <c r="G467" s="62"/>
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A468" s="27"/>
-      <c r="B468" s="27"/>
+      <c r="A468" s="62"/>
+      <c r="B468" s="62"/>
       <c r="C468" s="13" t="s">
         <v>91</v>
       </c>
@@ -9476,11 +9494,11 @@
       <c r="F468" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G468" s="27"/>
+      <c r="G468" s="62"/>
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A469" s="27"/>
-      <c r="B469" s="27"/>
+      <c r="A469" s="62"/>
+      <c r="B469" s="62"/>
       <c r="C469" s="13" t="s">
         <v>92</v>
       </c>
@@ -9493,11 +9511,11 @@
       <c r="F469" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G469" s="27"/>
+      <c r="G469" s="62"/>
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A470" s="27"/>
-      <c r="B470" s="27"/>
+      <c r="A470" s="62"/>
+      <c r="B470" s="62"/>
       <c r="C470" s="13" t="s">
         <v>93</v>
       </c>
@@ -9510,11 +9528,11 @@
       <c r="F470" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G470" s="27"/>
+      <c r="G470" s="62"/>
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A471" s="27"/>
-      <c r="B471" s="27"/>
+      <c r="A471" s="62"/>
+      <c r="B471" s="62"/>
       <c r="C471" s="13" t="s">
         <v>82</v>
       </c>
@@ -9527,11 +9545,11 @@
       <c r="F471" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G471" s="27"/>
+      <c r="G471" s="62"/>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A472" s="27"/>
-      <c r="B472" s="27"/>
+      <c r="A472" s="62"/>
+      <c r="B472" s="62"/>
       <c r="C472" s="13" t="s">
         <v>17</v>
       </c>
@@ -9544,26 +9562,28 @@
       <c r="F472" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G472" s="27"/>
+      <c r="G472" s="62"/>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A473" s="27"/>
-      <c r="B473" s="27"/>
+      <c r="A473" s="62"/>
+      <c r="B473" s="62"/>
       <c r="C473" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D473" s="14"/>
+      <c r="D473" s="14">
+        <v>0</v>
+      </c>
       <c r="E473" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F473" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G473" s="27"/>
+      <c r="G473" s="62"/>
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A474" s="27"/>
-      <c r="B474" s="27"/>
+      <c r="A474" s="62"/>
+      <c r="B474" s="62"/>
       <c r="C474" s="13" t="s">
         <v>32</v>
       </c>
@@ -9576,11 +9596,11 @@
       <c r="F474" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G474" s="27"/>
+      <c r="G474" s="62"/>
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A475" s="27"/>
-      <c r="B475" s="27"/>
+      <c r="A475" s="62"/>
+      <c r="B475" s="62"/>
       <c r="C475" s="13" t="s">
         <v>76</v>
       </c>
@@ -9593,11 +9613,11 @@
       <c r="F475" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G475" s="27"/>
+      <c r="G475" s="62"/>
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A476" s="27"/>
-      <c r="B476" s="27"/>
+      <c r="A476" s="62"/>
+      <c r="B476" s="62"/>
       <c r="C476" s="13" t="s">
         <v>110</v>
       </c>
@@ -9610,11 +9630,11 @@
       <c r="F476" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G476" s="27"/>
+      <c r="G476" s="62"/>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A477" s="29"/>
-      <c r="B477" s="29"/>
+      <c r="A477" s="59"/>
+      <c r="B477" s="59"/>
       <c r="C477" s="13" t="s">
         <v>115</v>
       </c>
@@ -9627,13 +9647,13 @@
       <c r="F477" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G477" s="29"/>
+      <c r="G477" s="59"/>
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A478" s="26">
+      <c r="A478" s="65">
         <v>36</v>
       </c>
-      <c r="B478" s="28" t="s">
+      <c r="B478" s="66" t="s">
         <v>123</v>
       </c>
       <c r="C478" s="13" t="s">
@@ -9648,13 +9668,13 @@
       <c r="F478" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G478" s="26" t="s">
+      <c r="G478" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A479" s="27"/>
-      <c r="B479" s="27"/>
+      <c r="A479" s="62"/>
+      <c r="B479" s="62"/>
       <c r="C479" s="13" t="s">
         <v>88</v>
       </c>
@@ -9667,11 +9687,11 @@
       <c r="F479" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G479" s="27"/>
+      <c r="G479" s="62"/>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A480" s="27"/>
-      <c r="B480" s="27"/>
+      <c r="A480" s="62"/>
+      <c r="B480" s="62"/>
       <c r="C480" s="13" t="s">
         <v>89</v>
       </c>
@@ -9684,11 +9704,11 @@
       <c r="F480" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G480" s="27"/>
+      <c r="G480" s="62"/>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A481" s="27"/>
-      <c r="B481" s="27"/>
+      <c r="A481" s="62"/>
+      <c r="B481" s="62"/>
       <c r="C481" s="13" t="s">
         <v>90</v>
       </c>
@@ -9701,11 +9721,11 @@
       <c r="F481" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G481" s="27"/>
+      <c r="G481" s="62"/>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A482" s="27"/>
-      <c r="B482" s="27"/>
+      <c r="A482" s="62"/>
+      <c r="B482" s="62"/>
       <c r="C482" s="13" t="s">
         <v>91</v>
       </c>
@@ -9718,11 +9738,11 @@
       <c r="F482" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G482" s="27"/>
+      <c r="G482" s="62"/>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A483" s="27"/>
-      <c r="B483" s="27"/>
+      <c r="A483" s="62"/>
+      <c r="B483" s="62"/>
       <c r="C483" s="13" t="s">
         <v>92</v>
       </c>
@@ -9735,11 +9755,11 @@
       <c r="F483" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G483" s="27"/>
+      <c r="G483" s="62"/>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A484" s="27"/>
-      <c r="B484" s="27"/>
+      <c r="A484" s="62"/>
+      <c r="B484" s="62"/>
       <c r="C484" s="13" t="s">
         <v>93</v>
       </c>
@@ -9752,11 +9772,11 @@
       <c r="F484" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G484" s="27"/>
+      <c r="G484" s="62"/>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A485" s="27"/>
-      <c r="B485" s="27"/>
+      <c r="A485" s="62"/>
+      <c r="B485" s="62"/>
       <c r="C485" s="13" t="s">
         <v>117</v>
       </c>
@@ -9769,11 +9789,11 @@
       <c r="F485" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G485" s="27"/>
+      <c r="G485" s="62"/>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A486" s="27"/>
-      <c r="B486" s="27"/>
+      <c r="A486" s="62"/>
+      <c r="B486" s="62"/>
       <c r="C486" s="13" t="s">
         <v>17</v>
       </c>
@@ -9786,26 +9806,28 @@
       <c r="F486" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G486" s="27"/>
+      <c r="G486" s="62"/>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A487" s="27"/>
-      <c r="B487" s="27"/>
+      <c r="A487" s="62"/>
+      <c r="B487" s="62"/>
       <c r="C487" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D487" s="14"/>
+      <c r="D487" s="14">
+        <v>0</v>
+      </c>
       <c r="E487" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F487" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G487" s="27"/>
+      <c r="G487" s="62"/>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A488" s="27"/>
-      <c r="B488" s="27"/>
+      <c r="A488" s="62"/>
+      <c r="B488" s="62"/>
       <c r="C488" s="13" t="s">
         <v>32</v>
       </c>
@@ -9818,11 +9840,11 @@
       <c r="F488" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G488" s="27"/>
+      <c r="G488" s="62"/>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A489" s="27"/>
-      <c r="B489" s="27"/>
+      <c r="A489" s="62"/>
+      <c r="B489" s="62"/>
       <c r="C489" s="13" t="s">
         <v>76</v>
       </c>
@@ -9835,11 +9857,11 @@
       <c r="F489" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G489" s="27"/>
+      <c r="G489" s="62"/>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A490" s="27"/>
-      <c r="B490" s="27"/>
+      <c r="A490" s="62"/>
+      <c r="B490" s="62"/>
       <c r="C490" s="13" t="s">
         <v>110</v>
       </c>
@@ -9852,13 +9874,13 @@
       <c r="F490" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G490" s="27"/>
+      <c r="G490" s="62"/>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A491" s="26">
+      <c r="A491" s="65">
         <v>37</v>
       </c>
-      <c r="B491" s="28" t="s">
+      <c r="B491" s="66" t="s">
         <v>124</v>
       </c>
       <c r="C491" s="13" t="s">
@@ -9873,13 +9895,13 @@
       <c r="F491" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G491" s="26" t="s">
+      <c r="G491" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A492" s="27"/>
-      <c r="B492" s="27"/>
+      <c r="A492" s="62"/>
+      <c r="B492" s="62"/>
       <c r="C492" s="13" t="s">
         <v>88</v>
       </c>
@@ -9892,11 +9914,11 @@
       <c r="F492" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G492" s="27"/>
+      <c r="G492" s="62"/>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A493" s="27"/>
-      <c r="B493" s="27"/>
+      <c r="A493" s="62"/>
+      <c r="B493" s="62"/>
       <c r="C493" s="13" t="s">
         <v>89</v>
       </c>
@@ -9909,11 +9931,11 @@
       <c r="F493" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G493" s="27"/>
+      <c r="G493" s="62"/>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A494" s="27"/>
-      <c r="B494" s="27"/>
+      <c r="A494" s="62"/>
+      <c r="B494" s="62"/>
       <c r="C494" s="13" t="s">
         <v>90</v>
       </c>
@@ -9926,11 +9948,11 @@
       <c r="F494" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G494" s="27"/>
+      <c r="G494" s="62"/>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A495" s="27"/>
-      <c r="B495" s="27"/>
+      <c r="A495" s="62"/>
+      <c r="B495" s="62"/>
       <c r="C495" s="13" t="s">
         <v>91</v>
       </c>
@@ -9943,11 +9965,11 @@
       <c r="F495" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G495" s="27"/>
+      <c r="G495" s="62"/>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A496" s="27"/>
-      <c r="B496" s="27"/>
+      <c r="A496" s="62"/>
+      <c r="B496" s="62"/>
       <c r="C496" s="13" t="s">
         <v>92</v>
       </c>
@@ -9960,11 +9982,11 @@
       <c r="F496" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G496" s="27"/>
+      <c r="G496" s="62"/>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A497" s="27"/>
-      <c r="B497" s="27"/>
+      <c r="A497" s="62"/>
+      <c r="B497" s="62"/>
       <c r="C497" s="13" t="s">
         <v>93</v>
       </c>
@@ -9977,11 +9999,11 @@
       <c r="F497" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G497" s="27"/>
+      <c r="G497" s="62"/>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A498" s="27"/>
-      <c r="B498" s="27"/>
+      <c r="A498" s="62"/>
+      <c r="B498" s="62"/>
       <c r="C498" s="13" t="s">
         <v>98</v>
       </c>
@@ -9994,11 +10016,11 @@
       <c r="F498" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G498" s="27"/>
+      <c r="G498" s="62"/>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A499" s="27"/>
-      <c r="B499" s="27"/>
+      <c r="A499" s="62"/>
+      <c r="B499" s="62"/>
       <c r="C499" s="13" t="s">
         <v>17</v>
       </c>
@@ -10011,26 +10033,28 @@
       <c r="F499" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G499" s="27"/>
+      <c r="G499" s="62"/>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A500" s="27"/>
-      <c r="B500" s="27"/>
+      <c r="A500" s="62"/>
+      <c r="B500" s="62"/>
       <c r="C500" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D500" s="14"/>
+      <c r="D500" s="14">
+        <v>0</v>
+      </c>
       <c r="E500" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F500" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G500" s="27"/>
+      <c r="G500" s="62"/>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A501" s="27"/>
-      <c r="B501" s="27"/>
+      <c r="A501" s="62"/>
+      <c r="B501" s="62"/>
       <c r="C501" s="13" t="s">
         <v>61</v>
       </c>
@@ -10043,11 +10067,11 @@
       <c r="F501" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G501" s="27"/>
+      <c r="G501" s="62"/>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A502" s="27"/>
-      <c r="B502" s="27"/>
+      <c r="A502" s="62"/>
+      <c r="B502" s="62"/>
       <c r="C502" s="13" t="s">
         <v>99</v>
       </c>
@@ -10060,11 +10084,11 @@
       <c r="F502" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G502" s="27"/>
+      <c r="G502" s="62"/>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A503" s="27"/>
-      <c r="B503" s="27"/>
+      <c r="A503" s="62"/>
+      <c r="B503" s="62"/>
       <c r="C503" s="13" t="s">
         <v>110</v>
       </c>
@@ -10077,13 +10101,13 @@
       <c r="F503" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G503" s="27"/>
+      <c r="G503" s="62"/>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A504" s="26">
+      <c r="A504" s="65">
         <v>38</v>
       </c>
-      <c r="B504" s="28" t="s">
+      <c r="B504" s="66" t="s">
         <v>125</v>
       </c>
       <c r="C504" s="13" t="s">
@@ -10098,13 +10122,13 @@
       <c r="F504" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G504" s="26" t="s">
+      <c r="G504" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A505" s="27"/>
-      <c r="B505" s="27"/>
+      <c r="A505" s="62"/>
+      <c r="B505" s="62"/>
       <c r="C505" s="13" t="s">
         <v>88</v>
       </c>
@@ -10117,11 +10141,11 @@
       <c r="F505" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G505" s="27"/>
+      <c r="G505" s="62"/>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A506" s="27"/>
-      <c r="B506" s="27"/>
+      <c r="A506" s="62"/>
+      <c r="B506" s="62"/>
       <c r="C506" s="13" t="s">
         <v>89</v>
       </c>
@@ -10134,11 +10158,11 @@
       <c r="F506" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G506" s="27"/>
+      <c r="G506" s="62"/>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A507" s="27"/>
-      <c r="B507" s="27"/>
+      <c r="A507" s="62"/>
+      <c r="B507" s="62"/>
       <c r="C507" s="13" t="s">
         <v>90</v>
       </c>
@@ -10151,11 +10175,11 @@
       <c r="F507" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G507" s="27"/>
+      <c r="G507" s="62"/>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A508" s="27"/>
-      <c r="B508" s="27"/>
+      <c r="A508" s="62"/>
+      <c r="B508" s="62"/>
       <c r="C508" s="13" t="s">
         <v>91</v>
       </c>
@@ -10168,11 +10192,11 @@
       <c r="F508" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G508" s="27"/>
+      <c r="G508" s="62"/>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A509" s="27"/>
-      <c r="B509" s="27"/>
+      <c r="A509" s="62"/>
+      <c r="B509" s="62"/>
       <c r="C509" s="13" t="s">
         <v>92</v>
       </c>
@@ -10185,11 +10209,11 @@
       <c r="F509" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G509" s="27"/>
+      <c r="G509" s="62"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A510" s="27"/>
-      <c r="B510" s="27"/>
+      <c r="A510" s="62"/>
+      <c r="B510" s="62"/>
       <c r="C510" s="13" t="s">
         <v>93</v>
       </c>
@@ -10202,11 +10226,11 @@
       <c r="F510" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G510" s="27"/>
+      <c r="G510" s="62"/>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A511" s="27"/>
-      <c r="B511" s="27"/>
+      <c r="A511" s="62"/>
+      <c r="B511" s="62"/>
       <c r="C511" s="13" t="s">
         <v>82</v>
       </c>
@@ -10219,11 +10243,11 @@
       <c r="F511" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G511" s="27"/>
+      <c r="G511" s="62"/>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A512" s="27"/>
-      <c r="B512" s="27"/>
+      <c r="A512" s="62"/>
+      <c r="B512" s="62"/>
       <c r="C512" s="13" t="s">
         <v>17</v>
       </c>
@@ -10236,26 +10260,28 @@
       <c r="F512" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G512" s="27"/>
+      <c r="G512" s="62"/>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A513" s="27"/>
-      <c r="B513" s="27"/>
+      <c r="A513" s="62"/>
+      <c r="B513" s="62"/>
       <c r="C513" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D513" s="14"/>
+      <c r="D513" s="14">
+        <v>0</v>
+      </c>
       <c r="E513" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F513" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G513" s="27"/>
+      <c r="G513" s="62"/>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A514" s="27"/>
-      <c r="B514" s="27"/>
+      <c r="A514" s="62"/>
+      <c r="B514" s="62"/>
       <c r="C514" s="13" t="s">
         <v>32</v>
       </c>
@@ -10268,11 +10294,11 @@
       <c r="F514" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G514" s="27"/>
+      <c r="G514" s="62"/>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A515" s="27"/>
-      <c r="B515" s="27"/>
+      <c r="A515" s="62"/>
+      <c r="B515" s="62"/>
       <c r="C515" s="13" t="s">
         <v>76</v>
       </c>
@@ -10285,11 +10311,11 @@
       <c r="F515" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G515" s="27"/>
+      <c r="G515" s="62"/>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A516" s="27"/>
-      <c r="B516" s="27"/>
+      <c r="A516" s="62"/>
+      <c r="B516" s="62"/>
       <c r="C516" s="13" t="s">
         <v>110</v>
       </c>
@@ -10302,11 +10328,11 @@
       <c r="F516" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G516" s="27"/>
+      <c r="G516" s="62"/>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A517" s="29"/>
-      <c r="B517" s="29"/>
+      <c r="A517" s="59"/>
+      <c r="B517" s="59"/>
       <c r="C517" s="13" t="s">
         <v>115</v>
       </c>
@@ -10319,13 +10345,13 @@
       <c r="F517" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G517" s="29"/>
+      <c r="G517" s="59"/>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A518" s="26">
+      <c r="A518" s="65">
         <v>39</v>
       </c>
-      <c r="B518" s="28" t="s">
+      <c r="B518" s="66" t="s">
         <v>126</v>
       </c>
       <c r="C518" s="13" t="s">
@@ -10340,13 +10366,13 @@
       <c r="F518" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G518" s="26" t="s">
+      <c r="G518" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A519" s="27"/>
-      <c r="B519" s="27"/>
+      <c r="A519" s="62"/>
+      <c r="B519" s="62"/>
       <c r="C519" s="13" t="s">
         <v>88</v>
       </c>
@@ -10359,11 +10385,11 @@
       <c r="F519" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G519" s="27"/>
+      <c r="G519" s="62"/>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A520" s="27"/>
-      <c r="B520" s="27"/>
+      <c r="A520" s="62"/>
+      <c r="B520" s="62"/>
       <c r="C520" s="13" t="s">
         <v>89</v>
       </c>
@@ -10376,11 +10402,11 @@
       <c r="F520" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G520" s="27"/>
+      <c r="G520" s="62"/>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A521" s="27"/>
-      <c r="B521" s="27"/>
+      <c r="A521" s="62"/>
+      <c r="B521" s="62"/>
       <c r="C521" s="13" t="s">
         <v>90</v>
       </c>
@@ -10393,11 +10419,11 @@
       <c r="F521" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G521" s="27"/>
+      <c r="G521" s="62"/>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A522" s="27"/>
-      <c r="B522" s="27"/>
+      <c r="A522" s="62"/>
+      <c r="B522" s="62"/>
       <c r="C522" s="13" t="s">
         <v>91</v>
       </c>
@@ -10410,11 +10436,11 @@
       <c r="F522" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G522" s="27"/>
+      <c r="G522" s="62"/>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A523" s="27"/>
-      <c r="B523" s="27"/>
+      <c r="A523" s="62"/>
+      <c r="B523" s="62"/>
       <c r="C523" s="13" t="s">
         <v>92</v>
       </c>
@@ -10427,11 +10453,11 @@
       <c r="F523" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G523" s="27"/>
+      <c r="G523" s="62"/>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A524" s="27"/>
-      <c r="B524" s="27"/>
+      <c r="A524" s="62"/>
+      <c r="B524" s="62"/>
       <c r="C524" s="13" t="s">
         <v>93</v>
       </c>
@@ -10444,11 +10470,11 @@
       <c r="F524" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G524" s="27"/>
+      <c r="G524" s="62"/>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A525" s="27"/>
-      <c r="B525" s="27"/>
+      <c r="A525" s="62"/>
+      <c r="B525" s="62"/>
       <c r="C525" s="13" t="s">
         <v>117</v>
       </c>
@@ -10461,11 +10487,11 @@
       <c r="F525" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G525" s="27"/>
+      <c r="G525" s="62"/>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A526" s="27"/>
-      <c r="B526" s="27"/>
+      <c r="A526" s="62"/>
+      <c r="B526" s="62"/>
       <c r="C526" s="13" t="s">
         <v>17</v>
       </c>
@@ -10478,26 +10504,28 @@
       <c r="F526" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G526" s="27"/>
+      <c r="G526" s="62"/>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A527" s="27"/>
-      <c r="B527" s="27"/>
+      <c r="A527" s="62"/>
+      <c r="B527" s="62"/>
       <c r="C527" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D527" s="14"/>
+      <c r="D527" s="14">
+        <v>0</v>
+      </c>
       <c r="E527" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F527" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G527" s="27"/>
+      <c r="G527" s="62"/>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A528" s="27"/>
-      <c r="B528" s="27"/>
+      <c r="A528" s="62"/>
+      <c r="B528" s="62"/>
       <c r="C528" s="13" t="s">
         <v>32</v>
       </c>
@@ -10510,11 +10538,11 @@
       <c r="F528" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G528" s="27"/>
+      <c r="G528" s="62"/>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A529" s="27"/>
-      <c r="B529" s="27"/>
+      <c r="A529" s="62"/>
+      <c r="B529" s="62"/>
       <c r="C529" s="13" t="s">
         <v>76</v>
       </c>
@@ -10527,11 +10555,11 @@
       <c r="F529" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G529" s="27"/>
+      <c r="G529" s="62"/>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A530" s="27"/>
-      <c r="B530" s="27"/>
+      <c r="A530" s="62"/>
+      <c r="B530" s="62"/>
       <c r="C530" s="13" t="s">
         <v>110</v>
       </c>
@@ -10544,13 +10572,13 @@
       <c r="F530" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="G530" s="27"/>
+      <c r="G530" s="62"/>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A531" s="26">
+      <c r="A531" s="65">
         <v>40</v>
       </c>
-      <c r="B531" s="28" t="s">
+      <c r="B531" s="66" t="s">
         <v>127</v>
       </c>
       <c r="C531" s="13" t="s">
@@ -10565,13 +10593,13 @@
       <c r="F531" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G531" s="26" t="s">
+      <c r="G531" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A532" s="27"/>
-      <c r="B532" s="27"/>
+      <c r="A532" s="62"/>
+      <c r="B532" s="62"/>
       <c r="C532" s="13" t="s">
         <v>88</v>
       </c>
@@ -10584,11 +10612,11 @@
       <c r="F532" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G532" s="27"/>
+      <c r="G532" s="62"/>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A533" s="27"/>
-      <c r="B533" s="27"/>
+      <c r="A533" s="62"/>
+      <c r="B533" s="62"/>
       <c r="C533" s="13" t="s">
         <v>89</v>
       </c>
@@ -10601,11 +10629,11 @@
       <c r="F533" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G533" s="27"/>
+      <c r="G533" s="62"/>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A534" s="27"/>
-      <c r="B534" s="27"/>
+      <c r="A534" s="62"/>
+      <c r="B534" s="62"/>
       <c r="C534" s="13" t="s">
         <v>90</v>
       </c>
@@ -10618,11 +10646,11 @@
       <c r="F534" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G534" s="27"/>
+      <c r="G534" s="62"/>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A535" s="27"/>
-      <c r="B535" s="27"/>
+      <c r="A535" s="62"/>
+      <c r="B535" s="62"/>
       <c r="C535" s="13" t="s">
         <v>91</v>
       </c>
@@ -10635,11 +10663,11 @@
       <c r="F535" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G535" s="27"/>
+      <c r="G535" s="62"/>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A536" s="27"/>
-      <c r="B536" s="27"/>
+      <c r="A536" s="62"/>
+      <c r="B536" s="62"/>
       <c r="C536" s="13" t="s">
         <v>92</v>
       </c>
@@ -10652,11 +10680,11 @@
       <c r="F536" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G536" s="27"/>
+      <c r="G536" s="62"/>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A537" s="27"/>
-      <c r="B537" s="27"/>
+      <c r="A537" s="62"/>
+      <c r="B537" s="62"/>
       <c r="C537" s="13" t="s">
         <v>93</v>
       </c>
@@ -10669,11 +10697,11 @@
       <c r="F537" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G537" s="27"/>
+      <c r="G537" s="62"/>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A538" s="27"/>
-      <c r="B538" s="27"/>
+      <c r="A538" s="62"/>
+      <c r="B538" s="62"/>
       <c r="C538" s="13" t="s">
         <v>98</v>
       </c>
@@ -10686,11 +10714,11 @@
       <c r="F538" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G538" s="27"/>
+      <c r="G538" s="62"/>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A539" s="27"/>
-      <c r="B539" s="27"/>
+      <c r="A539" s="62"/>
+      <c r="B539" s="62"/>
       <c r="C539" s="13" t="s">
         <v>17</v>
       </c>
@@ -10703,26 +10731,28 @@
       <c r="F539" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G539" s="27"/>
+      <c r="G539" s="62"/>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A540" s="27"/>
-      <c r="B540" s="27"/>
+      <c r="A540" s="62"/>
+      <c r="B540" s="62"/>
       <c r="C540" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D540" s="14"/>
+      <c r="D540" s="14">
+        <v>0</v>
+      </c>
       <c r="E540" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F540" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G540" s="27"/>
+      <c r="G540" s="62"/>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A541" s="27"/>
-      <c r="B541" s="27"/>
+      <c r="A541" s="62"/>
+      <c r="B541" s="62"/>
       <c r="C541" s="13" t="s">
         <v>61</v>
       </c>
@@ -10735,11 +10765,11 @@
       <c r="F541" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G541" s="27"/>
+      <c r="G541" s="62"/>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A542" s="27"/>
-      <c r="B542" s="27"/>
+      <c r="A542" s="62"/>
+      <c r="B542" s="62"/>
       <c r="C542" s="16" t="s">
         <v>99</v>
       </c>
@@ -10752,11 +10782,11 @@
       <c r="F542" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G542" s="27"/>
+      <c r="G542" s="62"/>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A543" s="29"/>
-      <c r="B543" s="29"/>
+      <c r="A543" s="59"/>
+      <c r="B543" s="59"/>
       <c r="C543" s="16" t="s">
         <v>110</v>
       </c>
@@ -10769,10 +10799,118 @@
       <c r="F543" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G543" s="29"/>
+      <c r="G543" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="120">
+    <mergeCell ref="A518:A530"/>
+    <mergeCell ref="B518:B530"/>
+    <mergeCell ref="G518:G530"/>
+    <mergeCell ref="A531:A543"/>
+    <mergeCell ref="B531:B543"/>
+    <mergeCell ref="G531:G543"/>
+    <mergeCell ref="A491:A503"/>
+    <mergeCell ref="B491:B503"/>
+    <mergeCell ref="G491:G503"/>
+    <mergeCell ref="A504:A517"/>
+    <mergeCell ref="B504:B517"/>
+    <mergeCell ref="G504:G517"/>
+    <mergeCell ref="A464:A477"/>
+    <mergeCell ref="B464:B477"/>
+    <mergeCell ref="G464:G477"/>
+    <mergeCell ref="A478:A490"/>
+    <mergeCell ref="B478:B490"/>
+    <mergeCell ref="G478:G490"/>
+    <mergeCell ref="A438:A450"/>
+    <mergeCell ref="B438:B450"/>
+    <mergeCell ref="G438:G450"/>
+    <mergeCell ref="A451:A463"/>
+    <mergeCell ref="B451:B463"/>
+    <mergeCell ref="G451:G463"/>
+    <mergeCell ref="A411:A423"/>
+    <mergeCell ref="B411:B423"/>
+    <mergeCell ref="G411:G423"/>
+    <mergeCell ref="A424:A437"/>
+    <mergeCell ref="B424:B437"/>
+    <mergeCell ref="G424:G437"/>
+    <mergeCell ref="A384:A397"/>
+    <mergeCell ref="B384:B397"/>
+    <mergeCell ref="G384:G397"/>
+    <mergeCell ref="A398:A410"/>
+    <mergeCell ref="B398:B410"/>
+    <mergeCell ref="G398:G410"/>
+    <mergeCell ref="A376:A380"/>
+    <mergeCell ref="B376:B380"/>
+    <mergeCell ref="G376:G380"/>
+    <mergeCell ref="A381:A383"/>
+    <mergeCell ref="B381:B383"/>
+    <mergeCell ref="G381:G383"/>
+    <mergeCell ref="A366:A370"/>
+    <mergeCell ref="B366:B370"/>
+    <mergeCell ref="G366:G370"/>
+    <mergeCell ref="A371:A375"/>
+    <mergeCell ref="B371:B375"/>
+    <mergeCell ref="G371:G375"/>
+    <mergeCell ref="A342:A353"/>
+    <mergeCell ref="B342:B353"/>
+    <mergeCell ref="G342:G353"/>
+    <mergeCell ref="A354:A365"/>
+    <mergeCell ref="B354:B365"/>
+    <mergeCell ref="G354:G365"/>
+    <mergeCell ref="A327:A329"/>
+    <mergeCell ref="B327:B329"/>
+    <mergeCell ref="G327:G329"/>
+    <mergeCell ref="A330:A341"/>
+    <mergeCell ref="B330:B341"/>
+    <mergeCell ref="G330:G341"/>
+    <mergeCell ref="A296:A313"/>
+    <mergeCell ref="B296:B313"/>
+    <mergeCell ref="G296:G313"/>
+    <mergeCell ref="A314:A325"/>
+    <mergeCell ref="B314:B325"/>
+    <mergeCell ref="G314:G326"/>
+    <mergeCell ref="A262:A278"/>
+    <mergeCell ref="B262:B278"/>
+    <mergeCell ref="G262:G278"/>
+    <mergeCell ref="A279:A295"/>
+    <mergeCell ref="B279:B295"/>
+    <mergeCell ref="G279:G295"/>
+    <mergeCell ref="A228:A244"/>
+    <mergeCell ref="B228:B244"/>
+    <mergeCell ref="G228:G244"/>
+    <mergeCell ref="A245:A261"/>
+    <mergeCell ref="B245:B261"/>
+    <mergeCell ref="G245:G261"/>
+    <mergeCell ref="A194:A210"/>
+    <mergeCell ref="B194:B210"/>
+    <mergeCell ref="G194:G210"/>
+    <mergeCell ref="A211:A227"/>
+    <mergeCell ref="B211:B227"/>
+    <mergeCell ref="G211:G227"/>
+    <mergeCell ref="A163:A176"/>
+    <mergeCell ref="B163:B176"/>
+    <mergeCell ref="G163:G176"/>
+    <mergeCell ref="A177:A193"/>
+    <mergeCell ref="B177:B193"/>
+    <mergeCell ref="G177:G193"/>
+    <mergeCell ref="A131:A148"/>
+    <mergeCell ref="B131:B148"/>
+    <mergeCell ref="G131:G148"/>
+    <mergeCell ref="A149:A162"/>
+    <mergeCell ref="B149:B162"/>
+    <mergeCell ref="G149:G162"/>
+    <mergeCell ref="A97:A113"/>
+    <mergeCell ref="B97:B113"/>
+    <mergeCell ref="G97:G113"/>
+    <mergeCell ref="A114:A130"/>
+    <mergeCell ref="B114:B130"/>
+    <mergeCell ref="G114:G130"/>
+    <mergeCell ref="A63:A79"/>
+    <mergeCell ref="B63:B79"/>
+    <mergeCell ref="G63:G79"/>
+    <mergeCell ref="A80:A96"/>
+    <mergeCell ref="B80:B96"/>
+    <mergeCell ref="G80:G96"/>
     <mergeCell ref="A29:A45"/>
     <mergeCell ref="B29:B45"/>
     <mergeCell ref="G29:G45"/>
@@ -10785,114 +10923,6 @@
     <mergeCell ref="A15:A28"/>
     <mergeCell ref="B15:B28"/>
     <mergeCell ref="G15:G28"/>
-    <mergeCell ref="A97:A113"/>
-    <mergeCell ref="B97:B113"/>
-    <mergeCell ref="G97:G113"/>
-    <mergeCell ref="A114:A130"/>
-    <mergeCell ref="B114:B130"/>
-    <mergeCell ref="G114:G130"/>
-    <mergeCell ref="A63:A79"/>
-    <mergeCell ref="B63:B79"/>
-    <mergeCell ref="G63:G79"/>
-    <mergeCell ref="A80:A96"/>
-    <mergeCell ref="B80:B96"/>
-    <mergeCell ref="G80:G96"/>
-    <mergeCell ref="A163:A176"/>
-    <mergeCell ref="B163:B176"/>
-    <mergeCell ref="G163:G176"/>
-    <mergeCell ref="A177:A193"/>
-    <mergeCell ref="B177:B193"/>
-    <mergeCell ref="G177:G193"/>
-    <mergeCell ref="A131:A148"/>
-    <mergeCell ref="B131:B148"/>
-    <mergeCell ref="G131:G148"/>
-    <mergeCell ref="A149:A162"/>
-    <mergeCell ref="B149:B162"/>
-    <mergeCell ref="G149:G162"/>
-    <mergeCell ref="A228:A244"/>
-    <mergeCell ref="B228:B244"/>
-    <mergeCell ref="G228:G244"/>
-    <mergeCell ref="A245:A261"/>
-    <mergeCell ref="B245:B261"/>
-    <mergeCell ref="G245:G261"/>
-    <mergeCell ref="A194:A210"/>
-    <mergeCell ref="B194:B210"/>
-    <mergeCell ref="G194:G210"/>
-    <mergeCell ref="A211:A227"/>
-    <mergeCell ref="B211:B227"/>
-    <mergeCell ref="G211:G227"/>
-    <mergeCell ref="A296:A313"/>
-    <mergeCell ref="B296:B313"/>
-    <mergeCell ref="G296:G313"/>
-    <mergeCell ref="A314:A325"/>
-    <mergeCell ref="B314:B325"/>
-    <mergeCell ref="G314:G326"/>
-    <mergeCell ref="A262:A278"/>
-    <mergeCell ref="B262:B278"/>
-    <mergeCell ref="G262:G278"/>
-    <mergeCell ref="A279:A295"/>
-    <mergeCell ref="B279:B295"/>
-    <mergeCell ref="G279:G295"/>
-    <mergeCell ref="A342:A353"/>
-    <mergeCell ref="B342:B353"/>
-    <mergeCell ref="G342:G353"/>
-    <mergeCell ref="A354:A365"/>
-    <mergeCell ref="B354:B365"/>
-    <mergeCell ref="G354:G365"/>
-    <mergeCell ref="A327:A329"/>
-    <mergeCell ref="B327:B329"/>
-    <mergeCell ref="G327:G329"/>
-    <mergeCell ref="A330:A341"/>
-    <mergeCell ref="B330:B341"/>
-    <mergeCell ref="G330:G341"/>
-    <mergeCell ref="A376:A380"/>
-    <mergeCell ref="B376:B380"/>
-    <mergeCell ref="G376:G380"/>
-    <mergeCell ref="A381:A383"/>
-    <mergeCell ref="B381:B383"/>
-    <mergeCell ref="G381:G383"/>
-    <mergeCell ref="A366:A370"/>
-    <mergeCell ref="B366:B370"/>
-    <mergeCell ref="G366:G370"/>
-    <mergeCell ref="A371:A375"/>
-    <mergeCell ref="B371:B375"/>
-    <mergeCell ref="G371:G375"/>
-    <mergeCell ref="A411:A423"/>
-    <mergeCell ref="B411:B423"/>
-    <mergeCell ref="G411:G423"/>
-    <mergeCell ref="A424:A437"/>
-    <mergeCell ref="B424:B437"/>
-    <mergeCell ref="G424:G437"/>
-    <mergeCell ref="A384:A397"/>
-    <mergeCell ref="B384:B397"/>
-    <mergeCell ref="G384:G397"/>
-    <mergeCell ref="A398:A410"/>
-    <mergeCell ref="B398:B410"/>
-    <mergeCell ref="G398:G410"/>
-    <mergeCell ref="A464:A477"/>
-    <mergeCell ref="B464:B477"/>
-    <mergeCell ref="G464:G477"/>
-    <mergeCell ref="A478:A490"/>
-    <mergeCell ref="B478:B490"/>
-    <mergeCell ref="G478:G490"/>
-    <mergeCell ref="A438:A450"/>
-    <mergeCell ref="B438:B450"/>
-    <mergeCell ref="G438:G450"/>
-    <mergeCell ref="A451:A463"/>
-    <mergeCell ref="B451:B463"/>
-    <mergeCell ref="G451:G463"/>
-    <mergeCell ref="A518:A530"/>
-    <mergeCell ref="B518:B530"/>
-    <mergeCell ref="G518:G530"/>
-    <mergeCell ref="A531:A543"/>
-    <mergeCell ref="B531:B543"/>
-    <mergeCell ref="G531:G543"/>
-    <mergeCell ref="A491:A503"/>
-    <mergeCell ref="B491:B503"/>
-    <mergeCell ref="G491:G503"/>
-    <mergeCell ref="A504:A517"/>
-    <mergeCell ref="B504:B517"/>
-    <mergeCell ref="G504:G517"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
